--- a/reports/history/build-4/Passed_Test_Cases.xlsx
+++ b/reports/history/build-4/Passed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2521" uniqueCount="1036">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2491" uniqueCount="1024">
   <si>
     <t>Test ID</t>
   </si>
@@ -76,12 +76,6 @@
     <t>Authentication Verification - Case 5</t>
   </si>
   <si>
-    <t>TC_AUTH_006</t>
-  </si>
-  <si>
-    <t>Authentication Verification - Case 6</t>
-  </si>
-  <si>
     <t>TC_AUTH_007</t>
   </si>
   <si>
@@ -196,10 +190,10 @@
     <t>Authentication Verification - Case 25</t>
   </si>
   <si>
-    <t>TC_AUTH_026</t>
-  </si>
-  <si>
-    <t>Authentication Verification - Case 26</t>
+    <t>TC_AUTH_027</t>
+  </si>
+  <si>
+    <t>Authentication Verification - Case 27</t>
   </si>
   <si>
     <t>TC_AUTH_028</t>
@@ -361,6 +355,12 @@
     <t>Authorization Verification - Case 13</t>
   </si>
   <si>
+    <t>TC_AZ_014</t>
+  </si>
+  <si>
+    <t>Authorization Verification - Case 14</t>
+  </si>
+  <si>
     <t>TC_AZ_015</t>
   </si>
   <si>
@@ -649,12 +649,6 @@
     <t>Profile Management Verification - Case 11</t>
   </si>
   <si>
-    <t>TC_PROF_012</t>
-  </si>
-  <si>
-    <t>Profile Management Verification - Case 12</t>
-  </si>
-  <si>
     <t>TC_PROF_013</t>
   </si>
   <si>
@@ -724,12 +718,6 @@
     <t>Navigation Verification - Case 3</t>
   </si>
   <si>
-    <t>TC_NAV_004</t>
-  </si>
-  <si>
-    <t>Navigation Verification - Case 4</t>
-  </si>
-  <si>
     <t>TC_NAV_005</t>
   </si>
   <si>
@@ -919,6 +907,12 @@
     <t>Dashboard Verification - Case 5</t>
   </si>
   <si>
+    <t>TC_DASH_006</t>
+  </si>
+  <si>
+    <t>Dashboard Verification - Case 6</t>
+  </si>
+  <si>
     <t>TC_DASH_007</t>
   </si>
   <si>
@@ -1084,6 +1078,12 @@
     <t>Forms Verification - Case 13</t>
   </si>
   <si>
+    <t>TC_FORM_014</t>
+  </si>
+  <si>
+    <t>Forms Verification - Case 14</t>
+  </si>
+  <si>
     <t>TC_FORM_015</t>
   </si>
   <si>
@@ -1327,6 +1327,12 @@
     <t>CRUD Operations Verification - Case 14</t>
   </si>
   <si>
+    <t>TC_CRUD_015</t>
+  </si>
+  <si>
+    <t>CRUD Operations Verification - Case 15</t>
+  </si>
+  <si>
     <t>TC_CRUD_016</t>
   </si>
   <si>
@@ -1369,6 +1375,12 @@
     <t>CRUD Operations Verification - Case 22</t>
   </si>
   <si>
+    <t>TC_CRUD_023</t>
+  </si>
+  <si>
+    <t>CRUD Operations Verification - Case 23</t>
+  </si>
+  <si>
     <t>TC_CRUD_024</t>
   </si>
   <si>
@@ -1393,12 +1405,6 @@
     <t>CRUD Operations Verification - Case 27</t>
   </si>
   <si>
-    <t>TC_CRUD_028</t>
-  </si>
-  <si>
-    <t>CRUD Operations Verification - Case 28</t>
-  </si>
-  <si>
     <t>TC_CRUD_029</t>
   </si>
   <si>
@@ -1435,6 +1441,12 @@
     <t>CRUD Operations Verification - Case 34</t>
   </si>
   <si>
+    <t>TC_CRUD_035</t>
+  </si>
+  <si>
+    <t>CRUD Operations Verification - Case 35</t>
+  </si>
+  <si>
     <t>TC_CRUD_036</t>
   </si>
   <si>
@@ -1510,12 +1522,6 @@
     <t>Search Verification - Case 7</t>
   </si>
   <si>
-    <t>TC_SRCH_008</t>
-  </si>
-  <si>
-    <t>Search Verification - Case 8</t>
-  </si>
-  <si>
     <t>TC_SRCH_009</t>
   </si>
   <si>
@@ -1699,12 +1705,6 @@
     <t>Filters Verification - Case 18</t>
   </si>
   <si>
-    <t>TC_FILT_019</t>
-  </si>
-  <si>
-    <t>Filters Verification - Case 19</t>
-  </si>
-  <si>
     <t>TC_FILT_020</t>
   </si>
   <si>
@@ -1942,12 +1942,6 @@
     <t>Input Validation Verification - Case 38</t>
   </si>
   <si>
-    <t>TC_VAL_039</t>
-  </si>
-  <si>
-    <t>Input Validation Verification - Case 39</t>
-  </si>
-  <si>
     <t>TC_VAL_040</t>
   </si>
   <si>
@@ -2566,12 +2560,6 @@
     <t>Accessibility Verification - Case 9</t>
   </si>
   <si>
-    <t>TC_ACC_010</t>
-  </si>
-  <si>
-    <t>Accessibility Verification - Case 10</t>
-  </si>
-  <si>
     <t>TC_ACC_011</t>
   </si>
   <si>
@@ -2788,12 +2776,6 @@
     <t>Performance Smoke Tests Verification - Case 15</t>
   </si>
   <si>
-    <t>TC_PERF_016</t>
-  </si>
-  <si>
-    <t>Performance Smoke Tests Verification - Case 16</t>
-  </si>
-  <si>
     <t>TC_PERF_017</t>
   </si>
   <si>
@@ -2923,24 +2905,12 @@
     <t>Regression Suite Verification - Case 17</t>
   </si>
   <si>
-    <t>TC_REGR_018</t>
-  </si>
-  <si>
-    <t>Regression Suite Verification - Case 18</t>
-  </si>
-  <si>
     <t>TC_REGR_019</t>
   </si>
   <si>
     <t>Regression Suite Verification - Case 19</t>
   </si>
   <si>
-    <t>TC_REGR_020</t>
-  </si>
-  <si>
-    <t>Regression Suite Verification - Case 20</t>
-  </si>
-  <si>
     <t>TC_REGR_021</t>
   </si>
   <si>
@@ -3101,12 +3071,6 @@
   </si>
   <si>
     <t>Regression Suite Verification - Case 47</t>
-  </si>
-  <si>
-    <t>TC_REGR_048</t>
-  </si>
-  <si>
-    <t>Regression Suite Verification - Case 48</t>
   </si>
   <si>
     <t>TC_REGR_049</t>
@@ -3509,7 +3473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F504"/>
+  <dimension ref="A1:F498"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -3556,7 +3520,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>216</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3576,7 +3540,7 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>141</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3596,7 +3560,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>253</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3616,7 +3580,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>210</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3636,7 +3600,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>282</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -3650,13 +3614,13 @@
         <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7">
-        <v>145</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -3670,13 +3634,13 @@
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8">
-        <v>225</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3690,7 +3654,7 @@
         <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -3710,13 +3674,13 @@
         <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -3730,13 +3694,13 @@
         <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11">
-        <v>116</v>
+        <v>299</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3750,13 +3714,13 @@
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
       <c r="F12">
-        <v>155</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -3770,13 +3734,13 @@
         <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13">
-        <v>183</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -3790,13 +3754,13 @@
         <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
       </c>
       <c r="F14">
-        <v>283</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -3810,13 +3774,13 @@
         <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15">
-        <v>154</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -3830,13 +3794,13 @@
         <v>40</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
       </c>
       <c r="F16">
-        <v>175</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -3850,13 +3814,13 @@
         <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
       <c r="F17">
-        <v>189</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -3870,13 +3834,13 @@
         <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
       </c>
       <c r="F18">
-        <v>218</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -3890,13 +3854,13 @@
         <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
       <c r="F19">
-        <v>149</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -3910,13 +3874,13 @@
         <v>48</v>
       </c>
       <c r="D20" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
       </c>
       <c r="F20">
-        <v>181</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -3930,13 +3894,13 @@
         <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
       </c>
       <c r="F21">
-        <v>260</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -3950,13 +3914,13 @@
         <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
       </c>
       <c r="F22">
-        <v>134</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -3970,13 +3934,13 @@
         <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
       </c>
       <c r="F23">
-        <v>220</v>
+        <v>244</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -3990,13 +3954,13 @@
         <v>56</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
       </c>
       <c r="F24">
-        <v>253</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -4010,13 +3974,13 @@
         <v>58</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
       </c>
       <c r="F25">
-        <v>186</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -4030,13 +3994,13 @@
         <v>60</v>
       </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
       </c>
       <c r="F26">
-        <v>249</v>
+        <v>198</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -4050,13 +4014,13 @@
         <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
       </c>
       <c r="F27">
-        <v>110</v>
+        <v>185</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -4070,13 +4034,13 @@
         <v>64</v>
       </c>
       <c r="D28" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
       </c>
       <c r="F28">
-        <v>239</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -4090,13 +4054,13 @@
         <v>66</v>
       </c>
       <c r="D29" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
       </c>
       <c r="F29">
-        <v>170</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -4110,13 +4074,13 @@
         <v>68</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
       </c>
       <c r="F30">
-        <v>246</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -4130,13 +4094,13 @@
         <v>70</v>
       </c>
       <c r="D31" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
       </c>
       <c r="F31">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -4150,13 +4114,13 @@
         <v>72</v>
       </c>
       <c r="D32" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
       </c>
       <c r="F32">
-        <v>164</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -4170,13 +4134,13 @@
         <v>74</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
       </c>
       <c r="F33">
-        <v>221</v>
+        <v>183</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -4190,13 +4154,13 @@
         <v>76</v>
       </c>
       <c r="D34" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
       </c>
       <c r="F34">
-        <v>143</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -4210,13 +4174,13 @@
         <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
       </c>
       <c r="F35">
-        <v>251</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -4230,13 +4194,13 @@
         <v>80</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
       </c>
       <c r="F36">
-        <v>204</v>
+        <v>279</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -4250,13 +4214,13 @@
         <v>82</v>
       </c>
       <c r="D37" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
       </c>
       <c r="F37">
-        <v>106</v>
+        <v>167</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -4270,13 +4234,13 @@
         <v>84</v>
       </c>
       <c r="D38" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
       </c>
       <c r="F38">
-        <v>296</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -4290,13 +4254,13 @@
         <v>86</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
       </c>
       <c r="F39">
-        <v>170</v>
+        <v>240</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -4304,10 +4268,10 @@
         <v>87</v>
       </c>
       <c r="B40" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="C40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D40" t="s">
         <v>9</v>
@@ -4316,27 +4280,27 @@
         <v>10</v>
       </c>
       <c r="F40">
-        <v>101</v>
+        <v>265</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B41" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C41" t="s">
         <v>91</v>
       </c>
       <c r="D41" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E41" t="s">
         <v>10</v>
       </c>
       <c r="F41">
-        <v>282</v>
+        <v>216</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -4344,19 +4308,19 @@
         <v>92</v>
       </c>
       <c r="B42" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C42" t="s">
         <v>93</v>
       </c>
       <c r="D42" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
       </c>
       <c r="F42">
-        <v>230</v>
+        <v>169</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -4364,19 +4328,19 @@
         <v>94</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C43" t="s">
         <v>95</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E43" t="s">
         <v>10</v>
       </c>
       <c r="F43">
-        <v>131</v>
+        <v>259</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -4384,19 +4348,19 @@
         <v>96</v>
       </c>
       <c r="B44" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C44" t="s">
         <v>97</v>
       </c>
       <c r="D44" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
       </c>
       <c r="F44">
-        <v>120</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -4404,19 +4368,19 @@
         <v>98</v>
       </c>
       <c r="B45" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C45" t="s">
         <v>99</v>
       </c>
       <c r="D45" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
       </c>
       <c r="F45">
-        <v>213</v>
+        <v>257</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -4424,19 +4388,19 @@
         <v>100</v>
       </c>
       <c r="B46" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C46" t="s">
         <v>101</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E46" t="s">
         <v>10</v>
       </c>
       <c r="F46">
-        <v>154</v>
+        <v>203</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -4444,19 +4408,19 @@
         <v>102</v>
       </c>
       <c r="B47" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C47" t="s">
         <v>103</v>
       </c>
       <c r="D47" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E47" t="s">
         <v>10</v>
       </c>
       <c r="F47">
-        <v>132</v>
+        <v>149</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -4464,19 +4428,19 @@
         <v>104</v>
       </c>
       <c r="B48" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C48" t="s">
         <v>105</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E48" t="s">
         <v>10</v>
       </c>
       <c r="F48">
-        <v>208</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -4484,19 +4448,19 @@
         <v>106</v>
       </c>
       <c r="B49" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C49" t="s">
         <v>107</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E49" t="s">
         <v>10</v>
       </c>
       <c r="F49">
-        <v>194</v>
+        <v>224</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -4504,19 +4468,19 @@
         <v>108</v>
       </c>
       <c r="B50" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C50" t="s">
         <v>109</v>
       </c>
       <c r="D50" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E50" t="s">
         <v>10</v>
       </c>
       <c r="F50">
-        <v>242</v>
+        <v>279</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -4524,19 +4488,19 @@
         <v>110</v>
       </c>
       <c r="B51" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C51" t="s">
         <v>111</v>
       </c>
       <c r="D51" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E51" t="s">
         <v>10</v>
       </c>
       <c r="F51">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -4544,19 +4508,19 @@
         <v>112</v>
       </c>
       <c r="B52" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C52" t="s">
         <v>113</v>
       </c>
       <c r="D52" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
       </c>
       <c r="F52">
-        <v>161</v>
+        <v>297</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -4564,19 +4528,19 @@
         <v>114</v>
       </c>
       <c r="B53" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C53" t="s">
         <v>115</v>
       </c>
       <c r="D53" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E53" t="s">
         <v>10</v>
       </c>
       <c r="F53">
-        <v>209</v>
+        <v>289</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -4584,7 +4548,7 @@
         <v>116</v>
       </c>
       <c r="B54" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C54" t="s">
         <v>117</v>
@@ -4596,7 +4560,7 @@
         <v>10</v>
       </c>
       <c r="F54">
-        <v>101</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -4604,7 +4568,7 @@
         <v>118</v>
       </c>
       <c r="B55" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C55" t="s">
         <v>119</v>
@@ -4616,7 +4580,7 @@
         <v>10</v>
       </c>
       <c r="F55">
-        <v>291</v>
+        <v>182</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -4624,7 +4588,7 @@
         <v>120</v>
       </c>
       <c r="B56" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C56" t="s">
         <v>121</v>
@@ -4636,7 +4600,7 @@
         <v>10</v>
       </c>
       <c r="F56">
-        <v>289</v>
+        <v>264</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -4644,7 +4608,7 @@
         <v>122</v>
       </c>
       <c r="B57" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C57" t="s">
         <v>123</v>
@@ -4656,7 +4620,7 @@
         <v>10</v>
       </c>
       <c r="F57">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -4664,7 +4628,7 @@
         <v>124</v>
       </c>
       <c r="B58" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C58" t="s">
         <v>125</v>
@@ -4676,7 +4640,7 @@
         <v>10</v>
       </c>
       <c r="F58">
-        <v>286</v>
+        <v>118</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -4684,7 +4648,7 @@
         <v>126</v>
       </c>
       <c r="B59" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C59" t="s">
         <v>127</v>
@@ -4696,7 +4660,7 @@
         <v>10</v>
       </c>
       <c r="F59">
-        <v>105</v>
+        <v>274</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -4704,7 +4668,7 @@
         <v>128</v>
       </c>
       <c r="B60" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C60" t="s">
         <v>129</v>
@@ -4716,7 +4680,7 @@
         <v>10</v>
       </c>
       <c r="F60">
-        <v>226</v>
+        <v>217</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -4724,7 +4688,7 @@
         <v>130</v>
       </c>
       <c r="B61" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C61" t="s">
         <v>131</v>
@@ -4736,7 +4700,7 @@
         <v>10</v>
       </c>
       <c r="F61">
-        <v>244</v>
+        <v>257</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -4744,7 +4708,7 @@
         <v>132</v>
       </c>
       <c r="B62" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C62" t="s">
         <v>133</v>
@@ -4756,7 +4720,7 @@
         <v>10</v>
       </c>
       <c r="F62">
-        <v>176</v>
+        <v>240</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -4764,7 +4728,7 @@
         <v>134</v>
       </c>
       <c r="B63" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C63" t="s">
         <v>135</v>
@@ -4776,7 +4740,7 @@
         <v>10</v>
       </c>
       <c r="F63">
-        <v>151</v>
+        <v>251</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -4784,7 +4748,7 @@
         <v>136</v>
       </c>
       <c r="B64" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C64" t="s">
         <v>137</v>
@@ -4796,7 +4760,7 @@
         <v>10</v>
       </c>
       <c r="F64">
-        <v>235</v>
+        <v>223</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -4804,7 +4768,7 @@
         <v>138</v>
       </c>
       <c r="B65" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C65" t="s">
         <v>139</v>
@@ -4816,7 +4780,7 @@
         <v>10</v>
       </c>
       <c r="F65">
-        <v>101</v>
+        <v>149</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -4824,7 +4788,7 @@
         <v>140</v>
       </c>
       <c r="B66" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C66" t="s">
         <v>141</v>
@@ -4836,7 +4800,7 @@
         <v>10</v>
       </c>
       <c r="F66">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -4844,7 +4808,7 @@
         <v>142</v>
       </c>
       <c r="B67" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C67" t="s">
         <v>143</v>
@@ -4856,7 +4820,7 @@
         <v>10</v>
       </c>
       <c r="F67">
-        <v>165</v>
+        <v>122</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -4864,7 +4828,7 @@
         <v>144</v>
       </c>
       <c r="B68" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C68" t="s">
         <v>145</v>
@@ -4876,7 +4840,7 @@
         <v>10</v>
       </c>
       <c r="F68">
-        <v>172</v>
+        <v>119</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -4884,7 +4848,7 @@
         <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C69" t="s">
         <v>147</v>
@@ -4896,7 +4860,7 @@
         <v>10</v>
       </c>
       <c r="F69">
-        <v>128</v>
+        <v>265</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -4916,7 +4880,7 @@
         <v>10</v>
       </c>
       <c r="F70">
-        <v>287</v>
+        <v>182</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -4936,7 +4900,7 @@
         <v>10</v>
       </c>
       <c r="F71">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -4956,7 +4920,7 @@
         <v>10</v>
       </c>
       <c r="F72">
-        <v>173</v>
+        <v>161</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -4976,7 +4940,7 @@
         <v>10</v>
       </c>
       <c r="F73">
-        <v>104</v>
+        <v>123</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -4996,7 +4960,7 @@
         <v>10</v>
       </c>
       <c r="F74">
-        <v>283</v>
+        <v>274</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -5016,7 +4980,7 @@
         <v>10</v>
       </c>
       <c r="F75">
-        <v>161</v>
+        <v>233</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -5036,7 +5000,7 @@
         <v>10</v>
       </c>
       <c r="F76">
-        <v>108</v>
+        <v>168</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -5056,7 +5020,7 @@
         <v>10</v>
       </c>
       <c r="F77">
-        <v>240</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -5076,7 +5040,7 @@
         <v>10</v>
       </c>
       <c r="F78">
-        <v>285</v>
+        <v>184</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -5096,7 +5060,7 @@
         <v>10</v>
       </c>
       <c r="F79">
-        <v>121</v>
+        <v>280</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -5116,7 +5080,7 @@
         <v>10</v>
       </c>
       <c r="F80">
-        <v>264</v>
+        <v>280</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -5136,7 +5100,7 @@
         <v>10</v>
       </c>
       <c r="F81">
-        <v>172</v>
+        <v>279</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -5156,7 +5120,7 @@
         <v>10</v>
       </c>
       <c r="F82">
-        <v>139</v>
+        <v>109</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -5176,7 +5140,7 @@
         <v>10</v>
       </c>
       <c r="F83">
-        <v>238</v>
+        <v>285</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -5196,7 +5160,7 @@
         <v>10</v>
       </c>
       <c r="F84">
-        <v>222</v>
+        <v>281</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -5216,7 +5180,7 @@
         <v>10</v>
       </c>
       <c r="F85">
-        <v>215</v>
+        <v>109</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -5236,7 +5200,7 @@
         <v>10</v>
       </c>
       <c r="F86">
-        <v>224</v>
+        <v>244</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -5256,7 +5220,7 @@
         <v>10</v>
       </c>
       <c r="F87">
-        <v>238</v>
+        <v>272</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -5276,7 +5240,7 @@
         <v>10</v>
       </c>
       <c r="F88">
-        <v>137</v>
+        <v>192</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -5296,7 +5260,7 @@
         <v>10</v>
       </c>
       <c r="F89">
-        <v>127</v>
+        <v>205</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -5316,7 +5280,7 @@
         <v>10</v>
       </c>
       <c r="F90">
-        <v>298</v>
+        <v>260</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -5336,7 +5300,7 @@
         <v>10</v>
       </c>
       <c r="F91">
-        <v>116</v>
+        <v>178</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -5356,7 +5320,7 @@
         <v>10</v>
       </c>
       <c r="F92">
-        <v>108</v>
+        <v>264</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -5376,7 +5340,7 @@
         <v>10</v>
       </c>
       <c r="F93">
-        <v>113</v>
+        <v>219</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -5396,7 +5360,7 @@
         <v>10</v>
       </c>
       <c r="F94">
-        <v>142</v>
+        <v>182</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -5416,7 +5380,7 @@
         <v>10</v>
       </c>
       <c r="F95">
-        <v>195</v>
+        <v>242</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -5436,7 +5400,7 @@
         <v>10</v>
       </c>
       <c r="F96">
-        <v>298</v>
+        <v>207</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -5456,7 +5420,7 @@
         <v>10</v>
       </c>
       <c r="F97">
-        <v>270</v>
+        <v>228</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -5476,7 +5440,7 @@
         <v>10</v>
       </c>
       <c r="F98">
-        <v>208</v>
+        <v>268</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -5496,7 +5460,7 @@
         <v>10</v>
       </c>
       <c r="F99">
-        <v>291</v>
+        <v>252</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -5516,7 +5480,7 @@
         <v>10</v>
       </c>
       <c r="F100">
-        <v>203</v>
+        <v>233</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -5530,13 +5494,13 @@
         <v>213</v>
       </c>
       <c r="D101" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E101" t="s">
         <v>10</v>
       </c>
       <c r="F101">
-        <v>295</v>
+        <v>275</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -5550,13 +5514,13 @@
         <v>215</v>
       </c>
       <c r="D102" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E102" t="s">
         <v>10</v>
       </c>
       <c r="F102">
-        <v>254</v>
+        <v>213</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -5570,13 +5534,13 @@
         <v>217</v>
       </c>
       <c r="D103" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E103" t="s">
         <v>10</v>
       </c>
       <c r="F103">
-        <v>244</v>
+        <v>142</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -5590,13 +5554,13 @@
         <v>219</v>
       </c>
       <c r="D104" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E104" t="s">
         <v>10</v>
       </c>
       <c r="F104">
-        <v>106</v>
+        <v>151</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -5610,13 +5574,13 @@
         <v>221</v>
       </c>
       <c r="D105" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E105" t="s">
         <v>10</v>
       </c>
       <c r="F105">
-        <v>204</v>
+        <v>116</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -5630,13 +5594,13 @@
         <v>223</v>
       </c>
       <c r="D106" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E106" t="s">
         <v>10</v>
       </c>
       <c r="F106">
-        <v>122</v>
+        <v>264</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -5650,13 +5614,13 @@
         <v>225</v>
       </c>
       <c r="D107" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E107" t="s">
         <v>10</v>
       </c>
       <c r="F107">
-        <v>259</v>
+        <v>226</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -5670,13 +5634,13 @@
         <v>227</v>
       </c>
       <c r="D108" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E108" t="s">
         <v>10</v>
       </c>
       <c r="F108">
-        <v>179</v>
+        <v>293</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -5684,39 +5648,39 @@
         <v>228</v>
       </c>
       <c r="B109" t="s">
-        <v>190</v>
+        <v>229</v>
       </c>
       <c r="C109" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D109" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E109" t="s">
         <v>10</v>
       </c>
       <c r="F109">
-        <v>203</v>
+        <v>122</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B110" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C110" t="s">
         <v>232</v>
       </c>
       <c r="D110" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E110" t="s">
         <v>10</v>
       </c>
       <c r="F110">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -5724,19 +5688,19 @@
         <v>233</v>
       </c>
       <c r="B111" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C111" t="s">
         <v>234</v>
       </c>
       <c r="D111" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E111" t="s">
         <v>10</v>
       </c>
       <c r="F111">
-        <v>280</v>
+        <v>163</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -5744,19 +5708,19 @@
         <v>235</v>
       </c>
       <c r="B112" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C112" t="s">
         <v>236</v>
       </c>
       <c r="D112" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E112" t="s">
         <v>10</v>
       </c>
       <c r="F112">
-        <v>290</v>
+        <v>160</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -5764,19 +5728,19 @@
         <v>237</v>
       </c>
       <c r="B113" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C113" t="s">
         <v>238</v>
       </c>
       <c r="D113" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E113" t="s">
         <v>10</v>
       </c>
       <c r="F113">
-        <v>249</v>
+        <v>119</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -5784,19 +5748,19 @@
         <v>239</v>
       </c>
       <c r="B114" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C114" t="s">
         <v>240</v>
       </c>
       <c r="D114" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E114" t="s">
         <v>10</v>
       </c>
       <c r="F114">
-        <v>292</v>
+        <v>281</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -5804,19 +5768,19 @@
         <v>241</v>
       </c>
       <c r="B115" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C115" t="s">
         <v>242</v>
       </c>
       <c r="D115" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E115" t="s">
         <v>10</v>
       </c>
       <c r="F115">
-        <v>173</v>
+        <v>162</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -5824,19 +5788,19 @@
         <v>243</v>
       </c>
       <c r="B116" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C116" t="s">
         <v>244</v>
       </c>
       <c r="D116" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E116" t="s">
         <v>10</v>
       </c>
       <c r="F116">
-        <v>277</v>
+        <v>120</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -5844,19 +5808,19 @@
         <v>245</v>
       </c>
       <c r="B117" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C117" t="s">
         <v>246</v>
       </c>
       <c r="D117" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E117" t="s">
         <v>10</v>
       </c>
       <c r="F117">
-        <v>279</v>
+        <v>106</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -5864,19 +5828,19 @@
         <v>247</v>
       </c>
       <c r="B118" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C118" t="s">
         <v>248</v>
       </c>
       <c r="D118" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E118" t="s">
         <v>10</v>
       </c>
       <c r="F118">
-        <v>267</v>
+        <v>169</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -5884,19 +5848,19 @@
         <v>249</v>
       </c>
       <c r="B119" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C119" t="s">
         <v>250</v>
       </c>
       <c r="D119" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E119" t="s">
         <v>10</v>
       </c>
       <c r="F119">
-        <v>187</v>
+        <v>256</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -5904,19 +5868,19 @@
         <v>251</v>
       </c>
       <c r="B120" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C120" t="s">
         <v>252</v>
       </c>
       <c r="D120" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E120" t="s">
         <v>10</v>
       </c>
       <c r="F120">
-        <v>297</v>
+        <v>173</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -5924,19 +5888,19 @@
         <v>253</v>
       </c>
       <c r="B121" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C121" t="s">
         <v>254</v>
       </c>
       <c r="D121" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E121" t="s">
         <v>10</v>
       </c>
       <c r="F121">
-        <v>164</v>
+        <v>197</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -5944,19 +5908,19 @@
         <v>255</v>
       </c>
       <c r="B122" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C122" t="s">
         <v>256</v>
       </c>
       <c r="D122" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E122" t="s">
         <v>10</v>
       </c>
       <c r="F122">
-        <v>282</v>
+        <v>132</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -5964,19 +5928,19 @@
         <v>257</v>
       </c>
       <c r="B123" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C123" t="s">
         <v>258</v>
       </c>
       <c r="D123" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E123" t="s">
         <v>10</v>
       </c>
       <c r="F123">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -5984,19 +5948,19 @@
         <v>259</v>
       </c>
       <c r="B124" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C124" t="s">
         <v>260</v>
       </c>
       <c r="D124" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E124" t="s">
         <v>10</v>
       </c>
       <c r="F124">
-        <v>238</v>
+        <v>156</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -6004,19 +5968,19 @@
         <v>261</v>
       </c>
       <c r="B125" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C125" t="s">
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E125" t="s">
         <v>10</v>
       </c>
       <c r="F125">
-        <v>179</v>
+        <v>298</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -6024,19 +5988,19 @@
         <v>263</v>
       </c>
       <c r="B126" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C126" t="s">
         <v>264</v>
       </c>
       <c r="D126" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E126" t="s">
         <v>10</v>
       </c>
       <c r="F126">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -6044,19 +6008,19 @@
         <v>265</v>
       </c>
       <c r="B127" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C127" t="s">
         <v>266</v>
       </c>
       <c r="D127" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E127" t="s">
         <v>10</v>
       </c>
       <c r="F127">
-        <v>268</v>
+        <v>218</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -6064,19 +6028,19 @@
         <v>267</v>
       </c>
       <c r="B128" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C128" t="s">
         <v>268</v>
       </c>
       <c r="D128" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E128" t="s">
         <v>10</v>
       </c>
       <c r="F128">
-        <v>150</v>
+        <v>244</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -6084,19 +6048,19 @@
         <v>269</v>
       </c>
       <c r="B129" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C129" t="s">
         <v>270</v>
       </c>
       <c r="D129" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E129" t="s">
         <v>10</v>
       </c>
       <c r="F129">
-        <v>272</v>
+        <v>184</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -6104,19 +6068,19 @@
         <v>271</v>
       </c>
       <c r="B130" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C130" t="s">
         <v>272</v>
       </c>
       <c r="D130" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E130" t="s">
         <v>10</v>
       </c>
       <c r="F130">
-        <v>136</v>
+        <v>218</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -6124,19 +6088,19 @@
         <v>273</v>
       </c>
       <c r="B131" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C131" t="s">
         <v>274</v>
       </c>
       <c r="D131" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E131" t="s">
         <v>10</v>
       </c>
       <c r="F131">
-        <v>224</v>
+        <v>100</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -6144,19 +6108,19 @@
         <v>275</v>
       </c>
       <c r="B132" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C132" t="s">
         <v>276</v>
       </c>
       <c r="D132" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E132" t="s">
         <v>10</v>
       </c>
       <c r="F132">
-        <v>121</v>
+        <v>244</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -6164,19 +6128,19 @@
         <v>277</v>
       </c>
       <c r="B133" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C133" t="s">
         <v>278</v>
       </c>
       <c r="D133" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E133" t="s">
         <v>10</v>
       </c>
       <c r="F133">
-        <v>257</v>
+        <v>132</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -6184,19 +6148,19 @@
         <v>279</v>
       </c>
       <c r="B134" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C134" t="s">
         <v>280</v>
       </c>
       <c r="D134" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E134" t="s">
         <v>10</v>
       </c>
       <c r="F134">
-        <v>178</v>
+        <v>209</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -6204,19 +6168,19 @@
         <v>281</v>
       </c>
       <c r="B135" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C135" t="s">
         <v>282</v>
       </c>
       <c r="D135" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E135" t="s">
         <v>10</v>
       </c>
       <c r="F135">
-        <v>291</v>
+        <v>239</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -6224,19 +6188,19 @@
         <v>283</v>
       </c>
       <c r="B136" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C136" t="s">
         <v>284</v>
       </c>
       <c r="D136" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E136" t="s">
         <v>10</v>
       </c>
       <c r="F136">
-        <v>120</v>
+        <v>252</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -6244,19 +6208,19 @@
         <v>285</v>
       </c>
       <c r="B137" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C137" t="s">
         <v>286</v>
       </c>
       <c r="D137" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E137" t="s">
         <v>10</v>
       </c>
       <c r="F137">
-        <v>148</v>
+        <v>247</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -6264,59 +6228,59 @@
         <v>287</v>
       </c>
       <c r="B138" t="s">
-        <v>231</v>
+        <v>288</v>
       </c>
       <c r="C138" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D138" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E138" t="s">
         <v>10</v>
       </c>
       <c r="F138">
-        <v>253</v>
+        <v>130</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B139" t="s">
-        <v>231</v>
+        <v>288</v>
       </c>
       <c r="C139" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D139" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E139" t="s">
         <v>10</v>
       </c>
       <c r="F139">
-        <v>290</v>
+        <v>299</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B140" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C140" t="s">
         <v>293</v>
       </c>
       <c r="D140" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E140" t="s">
         <v>10</v>
       </c>
       <c r="F140">
-        <v>282</v>
+        <v>222</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -6324,19 +6288,19 @@
         <v>294</v>
       </c>
       <c r="B141" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C141" t="s">
         <v>295</v>
       </c>
       <c r="D141" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E141" t="s">
         <v>10</v>
       </c>
       <c r="F141">
-        <v>101</v>
+        <v>207</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -6344,19 +6308,19 @@
         <v>296</v>
       </c>
       <c r="B142" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C142" t="s">
         <v>297</v>
       </c>
       <c r="D142" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E142" t="s">
         <v>10</v>
       </c>
       <c r="F142">
-        <v>253</v>
+        <v>206</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -6364,19 +6328,19 @@
         <v>298</v>
       </c>
       <c r="B143" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C143" t="s">
         <v>299</v>
       </c>
       <c r="D143" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E143" t="s">
         <v>10</v>
       </c>
       <c r="F143">
-        <v>109</v>
+        <v>234</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -6384,19 +6348,19 @@
         <v>300</v>
       </c>
       <c r="B144" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C144" t="s">
         <v>301</v>
       </c>
       <c r="D144" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E144" t="s">
         <v>10</v>
       </c>
       <c r="F144">
-        <v>104</v>
+        <v>267</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -6404,19 +6368,19 @@
         <v>302</v>
       </c>
       <c r="B145" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C145" t="s">
         <v>303</v>
       </c>
       <c r="D145" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E145" t="s">
         <v>10</v>
       </c>
       <c r="F145">
-        <v>248</v>
+        <v>115</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -6424,19 +6388,19 @@
         <v>304</v>
       </c>
       <c r="B146" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C146" t="s">
         <v>305</v>
       </c>
       <c r="D146" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E146" t="s">
         <v>10</v>
       </c>
       <c r="F146">
-        <v>224</v>
+        <v>100</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -6444,19 +6408,19 @@
         <v>306</v>
       </c>
       <c r="B147" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C147" t="s">
         <v>307</v>
       </c>
       <c r="D147" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E147" t="s">
         <v>10</v>
       </c>
       <c r="F147">
-        <v>200</v>
+        <v>253</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -6464,19 +6428,19 @@
         <v>308</v>
       </c>
       <c r="B148" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C148" t="s">
         <v>309</v>
       </c>
       <c r="D148" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E148" t="s">
         <v>10</v>
       </c>
       <c r="F148">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -6484,19 +6448,19 @@
         <v>310</v>
       </c>
       <c r="B149" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C149" t="s">
         <v>311</v>
       </c>
       <c r="D149" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E149" t="s">
         <v>10</v>
       </c>
       <c r="F149">
-        <v>287</v>
+        <v>195</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -6504,19 +6468,19 @@
         <v>312</v>
       </c>
       <c r="B150" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C150" t="s">
         <v>313</v>
       </c>
       <c r="D150" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E150" t="s">
         <v>10</v>
       </c>
       <c r="F150">
-        <v>116</v>
+        <v>254</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -6524,19 +6488,19 @@
         <v>314</v>
       </c>
       <c r="B151" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C151" t="s">
         <v>315</v>
       </c>
       <c r="D151" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E151" t="s">
         <v>10</v>
       </c>
       <c r="F151">
-        <v>157</v>
+        <v>230</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -6544,19 +6508,19 @@
         <v>316</v>
       </c>
       <c r="B152" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C152" t="s">
         <v>317</v>
       </c>
       <c r="D152" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E152" t="s">
         <v>10</v>
       </c>
       <c r="F152">
-        <v>143</v>
+        <v>184</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -6564,19 +6528,19 @@
         <v>318</v>
       </c>
       <c r="B153" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C153" t="s">
         <v>319</v>
       </c>
       <c r="D153" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E153" t="s">
         <v>10</v>
       </c>
       <c r="F153">
-        <v>187</v>
+        <v>157</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -6584,19 +6548,19 @@
         <v>320</v>
       </c>
       <c r="B154" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C154" t="s">
         <v>321</v>
       </c>
       <c r="D154" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E154" t="s">
         <v>10</v>
       </c>
       <c r="F154">
-        <v>253</v>
+        <v>126</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -6604,19 +6568,19 @@
         <v>322</v>
       </c>
       <c r="B155" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C155" t="s">
         <v>323</v>
       </c>
       <c r="D155" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E155" t="s">
         <v>10</v>
       </c>
       <c r="F155">
-        <v>202</v>
+        <v>154</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -6624,19 +6588,19 @@
         <v>324</v>
       </c>
       <c r="B156" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C156" t="s">
         <v>325</v>
       </c>
       <c r="D156" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E156" t="s">
         <v>10</v>
       </c>
       <c r="F156">
-        <v>259</v>
+        <v>178</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -6644,19 +6608,19 @@
         <v>326</v>
       </c>
       <c r="B157" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C157" t="s">
         <v>327</v>
       </c>
       <c r="D157" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E157" t="s">
         <v>10</v>
       </c>
       <c r="F157">
-        <v>114</v>
+        <v>295</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -6664,39 +6628,39 @@
         <v>328</v>
       </c>
       <c r="B158" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="C158" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D158" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E158" t="s">
         <v>10</v>
       </c>
       <c r="F158">
-        <v>232</v>
+        <v>195</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B159" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C159" t="s">
         <v>332</v>
       </c>
       <c r="D159" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E159" t="s">
         <v>10</v>
       </c>
       <c r="F159">
-        <v>113</v>
+        <v>102</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -6704,19 +6668,19 @@
         <v>333</v>
       </c>
       <c r="B160" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C160" t="s">
         <v>334</v>
       </c>
       <c r="D160" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E160" t="s">
         <v>10</v>
       </c>
       <c r="F160">
-        <v>249</v>
+        <v>160</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -6724,19 +6688,19 @@
         <v>335</v>
       </c>
       <c r="B161" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C161" t="s">
         <v>336</v>
       </c>
       <c r="D161" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E161" t="s">
         <v>10</v>
       </c>
       <c r="F161">
-        <v>235</v>
+        <v>148</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -6744,19 +6708,19 @@
         <v>337</v>
       </c>
       <c r="B162" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C162" t="s">
         <v>338</v>
       </c>
       <c r="D162" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E162" t="s">
         <v>10</v>
       </c>
       <c r="F162">
-        <v>264</v>
+        <v>294</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -6764,19 +6728,19 @@
         <v>339</v>
       </c>
       <c r="B163" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C163" t="s">
         <v>340</v>
       </c>
       <c r="D163" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E163" t="s">
         <v>10</v>
       </c>
       <c r="F163">
-        <v>212</v>
+        <v>132</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -6784,19 +6748,19 @@
         <v>341</v>
       </c>
       <c r="B164" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C164" t="s">
         <v>342</v>
       </c>
       <c r="D164" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E164" t="s">
         <v>10</v>
       </c>
       <c r="F164">
-        <v>273</v>
+        <v>113</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -6804,19 +6768,19 @@
         <v>343</v>
       </c>
       <c r="B165" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C165" t="s">
         <v>344</v>
       </c>
       <c r="D165" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E165" t="s">
         <v>10</v>
       </c>
       <c r="F165">
-        <v>104</v>
+        <v>180</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -6824,19 +6788,19 @@
         <v>345</v>
       </c>
       <c r="B166" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C166" t="s">
         <v>346</v>
       </c>
       <c r="D166" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E166" t="s">
         <v>10</v>
       </c>
       <c r="F166">
-        <v>206</v>
+        <v>268</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -6844,19 +6808,19 @@
         <v>347</v>
       </c>
       <c r="B167" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C167" t="s">
         <v>348</v>
       </c>
       <c r="D167" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E167" t="s">
         <v>10</v>
       </c>
       <c r="F167">
-        <v>145</v>
+        <v>129</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -6864,19 +6828,19 @@
         <v>349</v>
       </c>
       <c r="B168" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C168" t="s">
         <v>350</v>
       </c>
       <c r="D168" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E168" t="s">
         <v>10</v>
       </c>
       <c r="F168">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -6884,19 +6848,19 @@
         <v>351</v>
       </c>
       <c r="B169" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C169" t="s">
         <v>352</v>
       </c>
       <c r="D169" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E169" t="s">
         <v>10</v>
       </c>
       <c r="F169">
-        <v>118</v>
+        <v>209</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -6904,19 +6868,19 @@
         <v>353</v>
       </c>
       <c r="B170" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C170" t="s">
         <v>354</v>
       </c>
       <c r="D170" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E170" t="s">
         <v>10</v>
       </c>
       <c r="F170">
-        <v>113</v>
+        <v>218</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -6924,19 +6888,19 @@
         <v>355</v>
       </c>
       <c r="B171" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C171" t="s">
         <v>356</v>
       </c>
       <c r="D171" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E171" t="s">
         <v>10</v>
       </c>
       <c r="F171">
-        <v>209</v>
+        <v>189</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -6944,7 +6908,7 @@
         <v>357</v>
       </c>
       <c r="B172" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C172" t="s">
         <v>358</v>
@@ -6956,7 +6920,7 @@
         <v>10</v>
       </c>
       <c r="F172">
-        <v>215</v>
+        <v>149</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -6964,7 +6928,7 @@
         <v>359</v>
       </c>
       <c r="B173" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C173" t="s">
         <v>360</v>
@@ -6976,7 +6940,7 @@
         <v>10</v>
       </c>
       <c r="F173">
-        <v>194</v>
+        <v>171</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -6984,7 +6948,7 @@
         <v>361</v>
       </c>
       <c r="B174" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C174" t="s">
         <v>362</v>
@@ -6996,7 +6960,7 @@
         <v>10</v>
       </c>
       <c r="F174">
-        <v>166</v>
+        <v>119</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -7004,7 +6968,7 @@
         <v>363</v>
       </c>
       <c r="B175" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C175" t="s">
         <v>364</v>
@@ -7016,7 +6980,7 @@
         <v>10</v>
       </c>
       <c r="F175">
-        <v>155</v>
+        <v>216</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -7024,7 +6988,7 @@
         <v>365</v>
       </c>
       <c r="B176" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C176" t="s">
         <v>366</v>
@@ -7036,7 +7000,7 @@
         <v>10</v>
       </c>
       <c r="F176">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -7044,7 +7008,7 @@
         <v>367</v>
       </c>
       <c r="B177" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C177" t="s">
         <v>368</v>
@@ -7056,7 +7020,7 @@
         <v>10</v>
       </c>
       <c r="F177">
-        <v>260</v>
+        <v>139</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -7064,7 +7028,7 @@
         <v>369</v>
       </c>
       <c r="B178" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C178" t="s">
         <v>370</v>
@@ -7076,7 +7040,7 @@
         <v>10</v>
       </c>
       <c r="F178">
-        <v>105</v>
+        <v>175</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -7084,7 +7048,7 @@
         <v>371</v>
       </c>
       <c r="B179" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C179" t="s">
         <v>372</v>
@@ -7096,7 +7060,7 @@
         <v>10</v>
       </c>
       <c r="F179">
-        <v>134</v>
+        <v>202</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -7104,7 +7068,7 @@
         <v>373</v>
       </c>
       <c r="B180" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C180" t="s">
         <v>374</v>
@@ -7116,7 +7080,7 @@
         <v>10</v>
       </c>
       <c r="F180">
-        <v>203</v>
+        <v>166</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -7124,7 +7088,7 @@
         <v>375</v>
       </c>
       <c r="B181" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C181" t="s">
         <v>376</v>
@@ -7136,7 +7100,7 @@
         <v>10</v>
       </c>
       <c r="F181">
-        <v>216</v>
+        <v>188</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -7144,7 +7108,7 @@
         <v>377</v>
       </c>
       <c r="B182" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C182" t="s">
         <v>378</v>
@@ -7156,7 +7120,7 @@
         <v>10</v>
       </c>
       <c r="F182">
-        <v>206</v>
+        <v>189</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -7164,7 +7128,7 @@
         <v>379</v>
       </c>
       <c r="B183" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C183" t="s">
         <v>380</v>
@@ -7176,7 +7140,7 @@
         <v>10</v>
       </c>
       <c r="F183">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -7184,7 +7148,7 @@
         <v>381</v>
       </c>
       <c r="B184" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C184" t="s">
         <v>382</v>
@@ -7196,7 +7160,7 @@
         <v>10</v>
       </c>
       <c r="F184">
-        <v>213</v>
+        <v>122</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -7204,7 +7168,7 @@
         <v>383</v>
       </c>
       <c r="B185" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C185" t="s">
         <v>384</v>
@@ -7216,7 +7180,7 @@
         <v>10</v>
       </c>
       <c r="F185">
-        <v>127</v>
+        <v>106</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -7224,7 +7188,7 @@
         <v>385</v>
       </c>
       <c r="B186" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C186" t="s">
         <v>386</v>
@@ -7236,7 +7200,7 @@
         <v>10</v>
       </c>
       <c r="F186">
-        <v>145</v>
+        <v>288</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -7244,7 +7208,7 @@
         <v>387</v>
       </c>
       <c r="B187" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C187" t="s">
         <v>388</v>
@@ -7256,7 +7220,7 @@
         <v>10</v>
       </c>
       <c r="F187">
-        <v>153</v>
+        <v>226</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -7264,7 +7228,7 @@
         <v>389</v>
       </c>
       <c r="B188" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C188" t="s">
         <v>390</v>
@@ -7276,7 +7240,7 @@
         <v>10</v>
       </c>
       <c r="F188">
-        <v>165</v>
+        <v>146</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -7284,7 +7248,7 @@
         <v>391</v>
       </c>
       <c r="B189" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C189" t="s">
         <v>392</v>
@@ -7296,7 +7260,7 @@
         <v>10</v>
       </c>
       <c r="F189">
-        <v>185</v>
+        <v>230</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -7304,7 +7268,7 @@
         <v>393</v>
       </c>
       <c r="B190" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C190" t="s">
         <v>394</v>
@@ -7316,7 +7280,7 @@
         <v>10</v>
       </c>
       <c r="F190">
-        <v>191</v>
+        <v>159</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -7324,7 +7288,7 @@
         <v>395</v>
       </c>
       <c r="B191" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C191" t="s">
         <v>396</v>
@@ -7336,7 +7300,7 @@
         <v>10</v>
       </c>
       <c r="F191">
-        <v>228</v>
+        <v>111</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -7344,7 +7308,7 @@
         <v>397</v>
       </c>
       <c r="B192" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C192" t="s">
         <v>398</v>
@@ -7356,7 +7320,7 @@
         <v>10</v>
       </c>
       <c r="F192">
-        <v>225</v>
+        <v>258</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -7364,7 +7328,7 @@
         <v>399</v>
       </c>
       <c r="B193" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C193" t="s">
         <v>400</v>
@@ -7376,7 +7340,7 @@
         <v>10</v>
       </c>
       <c r="F193">
-        <v>231</v>
+        <v>222</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -7384,7 +7348,7 @@
         <v>401</v>
       </c>
       <c r="B194" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C194" t="s">
         <v>402</v>
@@ -7396,7 +7360,7 @@
         <v>10</v>
       </c>
       <c r="F194">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -7404,7 +7368,7 @@
         <v>403</v>
       </c>
       <c r="B195" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C195" t="s">
         <v>404</v>
@@ -7416,7 +7380,7 @@
         <v>10</v>
       </c>
       <c r="F195">
-        <v>206</v>
+        <v>195</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -7424,7 +7388,7 @@
         <v>405</v>
       </c>
       <c r="B196" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C196" t="s">
         <v>406</v>
@@ -7436,7 +7400,7 @@
         <v>10</v>
       </c>
       <c r="F196">
-        <v>233</v>
+        <v>226</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -7444,7 +7408,7 @@
         <v>407</v>
       </c>
       <c r="B197" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C197" t="s">
         <v>408</v>
@@ -7456,7 +7420,7 @@
         <v>10</v>
       </c>
       <c r="F197">
-        <v>259</v>
+        <v>272</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -7476,7 +7440,7 @@
         <v>10</v>
       </c>
       <c r="F198">
-        <v>231</v>
+        <v>157</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -7496,7 +7460,7 @@
         <v>10</v>
       </c>
       <c r="F199">
-        <v>216</v>
+        <v>287</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -7516,7 +7480,7 @@
         <v>10</v>
       </c>
       <c r="F200">
-        <v>238</v>
+        <v>266</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -7536,7 +7500,7 @@
         <v>10</v>
       </c>
       <c r="F201">
-        <v>299</v>
+        <v>210</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -7556,7 +7520,7 @@
         <v>10</v>
       </c>
       <c r="F202">
-        <v>287</v>
+        <v>211</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -7576,7 +7540,7 @@
         <v>10</v>
       </c>
       <c r="F203">
-        <v>120</v>
+        <v>152</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -7596,7 +7560,7 @@
         <v>10</v>
       </c>
       <c r="F204">
-        <v>271</v>
+        <v>257</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -7616,7 +7580,7 @@
         <v>10</v>
       </c>
       <c r="F205">
-        <v>295</v>
+        <v>111</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -7636,7 +7600,7 @@
         <v>10</v>
       </c>
       <c r="F206">
-        <v>192</v>
+        <v>223</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -7656,7 +7620,7 @@
         <v>10</v>
       </c>
       <c r="F207">
-        <v>272</v>
+        <v>199</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -7676,7 +7640,7 @@
         <v>10</v>
       </c>
       <c r="F208">
-        <v>226</v>
+        <v>134</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -7696,7 +7660,7 @@
         <v>10</v>
       </c>
       <c r="F209">
-        <v>280</v>
+        <v>254</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -7716,7 +7680,7 @@
         <v>10</v>
       </c>
       <c r="F210">
-        <v>125</v>
+        <v>157</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -7736,7 +7700,7 @@
         <v>10</v>
       </c>
       <c r="F211">
-        <v>177</v>
+        <v>274</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -7750,13 +7714,13 @@
         <v>439</v>
       </c>
       <c r="D212" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E212" t="s">
         <v>10</v>
       </c>
       <c r="F212">
-        <v>277</v>
+        <v>109</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -7770,13 +7734,13 @@
         <v>441</v>
       </c>
       <c r="D213" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E213" t="s">
         <v>10</v>
       </c>
       <c r="F213">
-        <v>286</v>
+        <v>158</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -7790,13 +7754,13 @@
         <v>443</v>
       </c>
       <c r="D214" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E214" t="s">
         <v>10</v>
       </c>
       <c r="F214">
-        <v>275</v>
+        <v>234</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -7810,13 +7774,13 @@
         <v>445</v>
       </c>
       <c r="D215" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E215" t="s">
         <v>10</v>
       </c>
       <c r="F215">
-        <v>230</v>
+        <v>176</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -7830,13 +7794,13 @@
         <v>447</v>
       </c>
       <c r="D216" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E216" t="s">
         <v>10</v>
       </c>
       <c r="F216">
-        <v>181</v>
+        <v>125</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -7850,13 +7814,13 @@
         <v>449</v>
       </c>
       <c r="D217" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E217" t="s">
         <v>10</v>
       </c>
       <c r="F217">
-        <v>219</v>
+        <v>249</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -7870,13 +7834,13 @@
         <v>451</v>
       </c>
       <c r="D218" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E218" t="s">
         <v>10</v>
       </c>
       <c r="F218">
-        <v>152</v>
+        <v>190</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -7890,13 +7854,13 @@
         <v>453</v>
       </c>
       <c r="D219" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E219" t="s">
         <v>10</v>
       </c>
       <c r="F219">
-        <v>255</v>
+        <v>183</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -7910,13 +7874,13 @@
         <v>455</v>
       </c>
       <c r="D220" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E220" t="s">
         <v>10</v>
       </c>
       <c r="F220">
-        <v>253</v>
+        <v>128</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -7930,13 +7894,13 @@
         <v>457</v>
       </c>
       <c r="D221" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E221" t="s">
         <v>10</v>
       </c>
       <c r="F221">
-        <v>135</v>
+        <v>242</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -7950,13 +7914,13 @@
         <v>459</v>
       </c>
       <c r="D222" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E222" t="s">
         <v>10</v>
       </c>
       <c r="F222">
-        <v>192</v>
+        <v>110</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -7970,13 +7934,13 @@
         <v>461</v>
       </c>
       <c r="D223" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E223" t="s">
         <v>10</v>
       </c>
       <c r="F223">
-        <v>275</v>
+        <v>182</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -7990,13 +7954,13 @@
         <v>463</v>
       </c>
       <c r="D224" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E224" t="s">
         <v>10</v>
       </c>
       <c r="F224">
-        <v>116</v>
+        <v>262</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -8010,13 +7974,13 @@
         <v>465</v>
       </c>
       <c r="D225" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E225" t="s">
         <v>10</v>
       </c>
       <c r="F225">
-        <v>127</v>
+        <v>264</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -8030,13 +7994,13 @@
         <v>467</v>
       </c>
       <c r="D226" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E226" t="s">
         <v>10</v>
       </c>
       <c r="F226">
-        <v>270</v>
+        <v>189</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -8050,13 +8014,13 @@
         <v>469</v>
       </c>
       <c r="D227" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E227" t="s">
         <v>10</v>
       </c>
       <c r="F227">
-        <v>172</v>
+        <v>185</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -8070,13 +8034,13 @@
         <v>471</v>
       </c>
       <c r="D228" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E228" t="s">
         <v>10</v>
       </c>
       <c r="F228">
-        <v>292</v>
+        <v>172</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -8090,13 +8054,13 @@
         <v>473</v>
       </c>
       <c r="D229" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E229" t="s">
         <v>10</v>
       </c>
       <c r="F229">
-        <v>228</v>
+        <v>113</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -8110,13 +8074,13 @@
         <v>475</v>
       </c>
       <c r="D230" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E230" t="s">
         <v>10</v>
       </c>
       <c r="F230">
-        <v>225</v>
+        <v>243</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -8130,13 +8094,13 @@
         <v>477</v>
       </c>
       <c r="D231" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E231" t="s">
         <v>10</v>
       </c>
       <c r="F231">
-        <v>155</v>
+        <v>115</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -8150,13 +8114,13 @@
         <v>479</v>
       </c>
       <c r="D232" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E232" t="s">
         <v>10</v>
       </c>
       <c r="F232">
-        <v>229</v>
+        <v>120</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -8170,13 +8134,13 @@
         <v>481</v>
       </c>
       <c r="D233" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E233" t="s">
         <v>10</v>
       </c>
       <c r="F233">
-        <v>236</v>
+        <v>164</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -8190,13 +8154,13 @@
         <v>483</v>
       </c>
       <c r="D234" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E234" t="s">
         <v>10</v>
       </c>
       <c r="F234">
-        <v>219</v>
+        <v>286</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -8204,59 +8168,59 @@
         <v>484</v>
       </c>
       <c r="B235" t="s">
+        <v>410</v>
+      </c>
+      <c r="C235" t="s">
         <v>485</v>
       </c>
-      <c r="C235" t="s">
-        <v>486</v>
-      </c>
       <c r="D235" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E235" t="s">
         <v>10</v>
       </c>
       <c r="F235">
-        <v>206</v>
+        <v>283</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
+        <v>486</v>
+      </c>
+      <c r="B236" t="s">
+        <v>410</v>
+      </c>
+      <c r="C236" t="s">
         <v>487</v>
       </c>
-      <c r="B236" t="s">
-        <v>485</v>
-      </c>
-      <c r="C236" t="s">
-        <v>488</v>
-      </c>
       <c r="D236" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E236" t="s">
         <v>10</v>
       </c>
       <c r="F236">
-        <v>225</v>
+        <v>122</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
+        <v>488</v>
+      </c>
+      <c r="B237" t="s">
         <v>489</v>
-      </c>
-      <c r="B237" t="s">
-        <v>485</v>
       </c>
       <c r="C237" t="s">
         <v>490</v>
       </c>
       <c r="D237" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E237" t="s">
         <v>10</v>
       </c>
       <c r="F237">
-        <v>224</v>
+        <v>139</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -8264,13 +8228,13 @@
         <v>491</v>
       </c>
       <c r="B238" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C238" t="s">
         <v>492</v>
       </c>
       <c r="D238" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E238" t="s">
         <v>10</v>
@@ -8284,19 +8248,19 @@
         <v>493</v>
       </c>
       <c r="B239" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C239" t="s">
         <v>494</v>
       </c>
       <c r="D239" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E239" t="s">
         <v>10</v>
       </c>
       <c r="F239">
-        <v>168</v>
+        <v>123</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -8304,19 +8268,19 @@
         <v>495</v>
       </c>
       <c r="B240" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C240" t="s">
         <v>496</v>
       </c>
       <c r="D240" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E240" t="s">
         <v>10</v>
       </c>
       <c r="F240">
-        <v>296</v>
+        <v>131</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -8324,19 +8288,19 @@
         <v>497</v>
       </c>
       <c r="B241" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C241" t="s">
         <v>498</v>
       </c>
       <c r="D241" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E241" t="s">
         <v>10</v>
       </c>
       <c r="F241">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -8344,19 +8308,19 @@
         <v>499</v>
       </c>
       <c r="B242" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C242" t="s">
         <v>500</v>
       </c>
       <c r="D242" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E242" t="s">
         <v>10</v>
       </c>
       <c r="F242">
-        <v>177</v>
+        <v>253</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -8364,19 +8328,19 @@
         <v>501</v>
       </c>
       <c r="B243" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C243" t="s">
         <v>502</v>
       </c>
       <c r="D243" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E243" t="s">
         <v>10</v>
       </c>
       <c r="F243">
-        <v>127</v>
+        <v>108</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -8384,19 +8348,19 @@
         <v>503</v>
       </c>
       <c r="B244" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C244" t="s">
         <v>504</v>
       </c>
       <c r="D244" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E244" t="s">
         <v>10</v>
       </c>
       <c r="F244">
-        <v>152</v>
+        <v>109</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -8404,19 +8368,19 @@
         <v>505</v>
       </c>
       <c r="B245" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C245" t="s">
         <v>506</v>
       </c>
       <c r="D245" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E245" t="s">
         <v>10</v>
       </c>
       <c r="F245">
-        <v>144</v>
+        <v>195</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -8424,19 +8388,19 @@
         <v>507</v>
       </c>
       <c r="B246" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C246" t="s">
         <v>508</v>
       </c>
       <c r="D246" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E246" t="s">
         <v>10</v>
       </c>
       <c r="F246">
-        <v>208</v>
+        <v>160</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -8444,19 +8408,19 @@
         <v>509</v>
       </c>
       <c r="B247" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C247" t="s">
         <v>510</v>
       </c>
       <c r="D247" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E247" t="s">
         <v>10</v>
       </c>
       <c r="F247">
-        <v>130</v>
+        <v>172</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -8464,19 +8428,19 @@
         <v>511</v>
       </c>
       <c r="B248" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C248" t="s">
         <v>512</v>
       </c>
       <c r="D248" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E248" t="s">
         <v>10</v>
       </c>
       <c r="F248">
-        <v>221</v>
+        <v>249</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -8484,19 +8448,19 @@
         <v>513</v>
       </c>
       <c r="B249" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C249" t="s">
         <v>514</v>
       </c>
       <c r="D249" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E249" t="s">
         <v>10</v>
       </c>
       <c r="F249">
-        <v>277</v>
+        <v>201</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -8504,19 +8468,19 @@
         <v>515</v>
       </c>
       <c r="B250" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C250" t="s">
         <v>516</v>
       </c>
       <c r="D250" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E250" t="s">
         <v>10</v>
       </c>
       <c r="F250">
-        <v>169</v>
+        <v>193</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -8524,19 +8488,19 @@
         <v>517</v>
       </c>
       <c r="B251" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C251" t="s">
         <v>518</v>
       </c>
       <c r="D251" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E251" t="s">
         <v>10</v>
       </c>
       <c r="F251">
-        <v>179</v>
+        <v>117</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -8544,19 +8508,19 @@
         <v>519</v>
       </c>
       <c r="B252" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C252" t="s">
         <v>520</v>
       </c>
       <c r="D252" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E252" t="s">
         <v>10</v>
       </c>
       <c r="F252">
-        <v>193</v>
+        <v>125</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -8564,19 +8528,19 @@
         <v>521</v>
       </c>
       <c r="B253" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C253" t="s">
         <v>522</v>
       </c>
       <c r="D253" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E253" t="s">
         <v>10</v>
       </c>
       <c r="F253">
-        <v>226</v>
+        <v>263</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -8584,19 +8548,19 @@
         <v>523</v>
       </c>
       <c r="B254" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C254" t="s">
         <v>524</v>
       </c>
       <c r="D254" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E254" t="s">
         <v>10</v>
       </c>
       <c r="F254">
-        <v>287</v>
+        <v>294</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -8604,39 +8568,39 @@
         <v>525</v>
       </c>
       <c r="B255" t="s">
+        <v>489</v>
+      </c>
+      <c r="C255" t="s">
         <v>526</v>
       </c>
-      <c r="C255" t="s">
-        <v>527</v>
-      </c>
       <c r="D255" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E255" t="s">
         <v>10</v>
       </c>
       <c r="F255">
-        <v>132</v>
+        <v>116</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
+        <v>527</v>
+      </c>
+      <c r="B256" t="s">
         <v>528</v>
-      </c>
-      <c r="B256" t="s">
-        <v>526</v>
       </c>
       <c r="C256" t="s">
         <v>529</v>
       </c>
       <c r="D256" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E256" t="s">
         <v>10</v>
       </c>
       <c r="F256">
-        <v>267</v>
+        <v>234</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -8644,19 +8608,19 @@
         <v>530</v>
       </c>
       <c r="B257" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C257" t="s">
         <v>531</v>
       </c>
       <c r="D257" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E257" t="s">
         <v>10</v>
       </c>
       <c r="F257">
-        <v>259</v>
+        <v>296</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -8664,19 +8628,19 @@
         <v>532</v>
       </c>
       <c r="B258" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C258" t="s">
         <v>533</v>
       </c>
       <c r="D258" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E258" t="s">
         <v>10</v>
       </c>
       <c r="F258">
-        <v>101</v>
+        <v>258</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -8684,19 +8648,19 @@
         <v>534</v>
       </c>
       <c r="B259" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C259" t="s">
         <v>535</v>
       </c>
       <c r="D259" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E259" t="s">
         <v>10</v>
       </c>
       <c r="F259">
-        <v>271</v>
+        <v>202</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -8704,19 +8668,19 @@
         <v>536</v>
       </c>
       <c r="B260" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C260" t="s">
         <v>537</v>
       </c>
       <c r="D260" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E260" t="s">
         <v>10</v>
       </c>
       <c r="F260">
-        <v>291</v>
+        <v>148</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -8724,19 +8688,19 @@
         <v>538</v>
       </c>
       <c r="B261" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C261" t="s">
         <v>539</v>
       </c>
       <c r="D261" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E261" t="s">
         <v>10</v>
       </c>
       <c r="F261">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -8744,19 +8708,19 @@
         <v>540</v>
       </c>
       <c r="B262" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C262" t="s">
         <v>541</v>
       </c>
       <c r="D262" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E262" t="s">
         <v>10</v>
       </c>
       <c r="F262">
-        <v>119</v>
+        <v>244</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -8764,19 +8728,19 @@
         <v>542</v>
       </c>
       <c r="B263" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C263" t="s">
         <v>543</v>
       </c>
       <c r="D263" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E263" t="s">
         <v>10</v>
       </c>
       <c r="F263">
-        <v>261</v>
+        <v>106</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -8784,19 +8748,19 @@
         <v>544</v>
       </c>
       <c r="B264" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C264" t="s">
         <v>545</v>
       </c>
       <c r="D264" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E264" t="s">
         <v>10</v>
       </c>
       <c r="F264">
-        <v>212</v>
+        <v>165</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -8804,19 +8768,19 @@
         <v>546</v>
       </c>
       <c r="B265" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C265" t="s">
         <v>547</v>
       </c>
       <c r="D265" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E265" t="s">
         <v>10</v>
       </c>
       <c r="F265">
-        <v>279</v>
+        <v>257</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -8824,19 +8788,19 @@
         <v>548</v>
       </c>
       <c r="B266" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C266" t="s">
         <v>549</v>
       </c>
       <c r="D266" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E266" t="s">
         <v>10</v>
       </c>
       <c r="F266">
-        <v>163</v>
+        <v>205</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -8844,19 +8808,19 @@
         <v>550</v>
       </c>
       <c r="B267" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C267" t="s">
         <v>551</v>
       </c>
       <c r="D267" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E267" t="s">
         <v>10</v>
       </c>
       <c r="F267">
-        <v>213</v>
+        <v>105</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -8864,19 +8828,19 @@
         <v>552</v>
       </c>
       <c r="B268" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C268" t="s">
         <v>553</v>
       </c>
       <c r="D268" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E268" t="s">
         <v>10</v>
       </c>
       <c r="F268">
-        <v>230</v>
+        <v>157</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -8884,19 +8848,19 @@
         <v>554</v>
       </c>
       <c r="B269" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C269" t="s">
         <v>555</v>
       </c>
       <c r="D269" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E269" t="s">
         <v>10</v>
       </c>
       <c r="F269">
-        <v>252</v>
+        <v>156</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -8904,19 +8868,19 @@
         <v>556</v>
       </c>
       <c r="B270" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C270" t="s">
         <v>557</v>
       </c>
       <c r="D270" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E270" t="s">
         <v>10</v>
       </c>
       <c r="F270">
-        <v>279</v>
+        <v>115</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -8924,19 +8888,19 @@
         <v>558</v>
       </c>
       <c r="B271" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C271" t="s">
         <v>559</v>
       </c>
       <c r="D271" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E271" t="s">
         <v>10</v>
       </c>
       <c r="F271">
-        <v>183</v>
+        <v>150</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -8944,19 +8908,19 @@
         <v>560</v>
       </c>
       <c r="B272" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C272" t="s">
         <v>561</v>
       </c>
       <c r="D272" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E272" t="s">
         <v>10</v>
       </c>
       <c r="F272">
-        <v>260</v>
+        <v>158</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -8964,19 +8928,19 @@
         <v>562</v>
       </c>
       <c r="B273" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C273" t="s">
         <v>563</v>
       </c>
       <c r="D273" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E273" t="s">
         <v>10</v>
       </c>
       <c r="F273">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -8984,7 +8948,7 @@
         <v>564</v>
       </c>
       <c r="B274" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C274" t="s">
         <v>565</v>
@@ -8996,7 +8960,7 @@
         <v>10</v>
       </c>
       <c r="F274">
-        <v>202</v>
+        <v>191</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -9016,7 +8980,7 @@
         <v>10</v>
       </c>
       <c r="F275">
-        <v>249</v>
+        <v>169</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -9036,7 +9000,7 @@
         <v>10</v>
       </c>
       <c r="F276">
-        <v>180</v>
+        <v>273</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -9056,7 +9020,7 @@
         <v>10</v>
       </c>
       <c r="F277">
-        <v>269</v>
+        <v>149</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -9076,7 +9040,7 @@
         <v>10</v>
       </c>
       <c r="F278">
-        <v>257</v>
+        <v>147</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -9096,7 +9060,7 @@
         <v>10</v>
       </c>
       <c r="F279">
-        <v>166</v>
+        <v>156</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -9116,7 +9080,7 @@
         <v>10</v>
       </c>
       <c r="F280">
-        <v>143</v>
+        <v>232</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -9136,7 +9100,7 @@
         <v>10</v>
       </c>
       <c r="F281">
-        <v>245</v>
+        <v>202</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -9156,7 +9120,7 @@
         <v>10</v>
       </c>
       <c r="F282">
-        <v>119</v>
+        <v>270</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -9176,7 +9140,7 @@
         <v>10</v>
       </c>
       <c r="F283">
-        <v>237</v>
+        <v>186</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -9196,7 +9160,7 @@
         <v>10</v>
       </c>
       <c r="F284">
-        <v>147</v>
+        <v>166</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -9216,7 +9180,7 @@
         <v>10</v>
       </c>
       <c r="F285">
-        <v>168</v>
+        <v>218</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -9236,7 +9200,7 @@
         <v>10</v>
       </c>
       <c r="F286">
-        <v>125</v>
+        <v>235</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -9256,7 +9220,7 @@
         <v>10</v>
       </c>
       <c r="F287">
-        <v>102</v>
+        <v>284</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -9276,7 +9240,7 @@
         <v>10</v>
       </c>
       <c r="F288">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -9296,7 +9260,7 @@
         <v>10</v>
       </c>
       <c r="F289">
-        <v>149</v>
+        <v>178</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -9316,7 +9280,7 @@
         <v>10</v>
       </c>
       <c r="F290">
-        <v>148</v>
+        <v>230</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -9336,7 +9300,7 @@
         <v>10</v>
       </c>
       <c r="F291">
-        <v>191</v>
+        <v>153</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -9356,7 +9320,7 @@
         <v>10</v>
       </c>
       <c r="F292">
-        <v>297</v>
+        <v>211</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -9376,7 +9340,7 @@
         <v>10</v>
       </c>
       <c r="F293">
-        <v>224</v>
+        <v>153</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -9396,7 +9360,7 @@
         <v>10</v>
       </c>
       <c r="F294">
-        <v>211</v>
+        <v>226</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -9416,7 +9380,7 @@
         <v>10</v>
       </c>
       <c r="F295">
-        <v>196</v>
+        <v>262</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -9436,7 +9400,7 @@
         <v>10</v>
       </c>
       <c r="F296">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -9456,7 +9420,7 @@
         <v>10</v>
       </c>
       <c r="F297">
-        <v>251</v>
+        <v>209</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -9476,7 +9440,7 @@
         <v>10</v>
       </c>
       <c r="F298">
-        <v>205</v>
+        <v>298</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -9496,7 +9460,7 @@
         <v>10</v>
       </c>
       <c r="F299">
-        <v>153</v>
+        <v>135</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -9516,7 +9480,7 @@
         <v>10</v>
       </c>
       <c r="F300">
-        <v>152</v>
+        <v>131</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -9536,7 +9500,7 @@
         <v>10</v>
       </c>
       <c r="F301">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -9556,7 +9520,7 @@
         <v>10</v>
       </c>
       <c r="F302">
-        <v>154</v>
+        <v>283</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -9576,7 +9540,7 @@
         <v>10</v>
       </c>
       <c r="F303">
-        <v>252</v>
+        <v>200</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -9596,7 +9560,7 @@
         <v>10</v>
       </c>
       <c r="F304">
-        <v>128</v>
+        <v>219</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -9616,7 +9580,7 @@
         <v>10</v>
       </c>
       <c r="F305">
-        <v>234</v>
+        <v>150</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -9636,7 +9600,7 @@
         <v>10</v>
       </c>
       <c r="F306">
-        <v>120</v>
+        <v>219</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -9656,7 +9620,7 @@
         <v>10</v>
       </c>
       <c r="F307">
-        <v>241</v>
+        <v>295</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -9676,7 +9640,7 @@
         <v>10</v>
       </c>
       <c r="F308">
-        <v>156</v>
+        <v>213</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -9696,7 +9660,7 @@
         <v>10</v>
       </c>
       <c r="F309">
-        <v>206</v>
+        <v>175</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -9716,7 +9680,7 @@
         <v>10</v>
       </c>
       <c r="F310">
-        <v>183</v>
+        <v>136</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -9736,7 +9700,7 @@
         <v>10</v>
       </c>
       <c r="F311">
-        <v>169</v>
+        <v>123</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -9756,7 +9720,7 @@
         <v>10</v>
       </c>
       <c r="F312">
-        <v>102</v>
+        <v>253</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -9770,13 +9734,13 @@
         <v>644</v>
       </c>
       <c r="D313" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E313" t="s">
         <v>10</v>
       </c>
       <c r="F313">
-        <v>278</v>
+        <v>296</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -9784,10 +9748,10 @@
         <v>645</v>
       </c>
       <c r="B314" t="s">
-        <v>567</v>
+        <v>646</v>
       </c>
       <c r="C314" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D314" t="s">
         <v>9</v>
@@ -9796,27 +9760,27 @@
         <v>10</v>
       </c>
       <c r="F314">
-        <v>100</v>
+        <v>124</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B315" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C315" t="s">
         <v>649</v>
       </c>
       <c r="D315" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E315" t="s">
         <v>10</v>
       </c>
       <c r="F315">
-        <v>191</v>
+        <v>290</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -9824,19 +9788,19 @@
         <v>650</v>
       </c>
       <c r="B316" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C316" t="s">
         <v>651</v>
       </c>
       <c r="D316" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E316" t="s">
         <v>10</v>
       </c>
       <c r="F316">
-        <v>230</v>
+        <v>260</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -9844,19 +9808,19 @@
         <v>652</v>
       </c>
       <c r="B317" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C317" t="s">
         <v>653</v>
       </c>
       <c r="D317" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E317" t="s">
         <v>10</v>
       </c>
       <c r="F317">
-        <v>236</v>
+        <v>299</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -9864,19 +9828,19 @@
         <v>654</v>
       </c>
       <c r="B318" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C318" t="s">
         <v>655</v>
       </c>
       <c r="D318" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E318" t="s">
         <v>10</v>
       </c>
       <c r="F318">
-        <v>146</v>
+        <v>218</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -9884,19 +9848,19 @@
         <v>656</v>
       </c>
       <c r="B319" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C319" t="s">
         <v>657</v>
       </c>
       <c r="D319" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E319" t="s">
         <v>10</v>
       </c>
       <c r="F319">
-        <v>273</v>
+        <v>250</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -9904,19 +9868,19 @@
         <v>658</v>
       </c>
       <c r="B320" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C320" t="s">
         <v>659</v>
       </c>
       <c r="D320" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E320" t="s">
         <v>10</v>
       </c>
       <c r="F320">
-        <v>262</v>
+        <v>219</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -9924,19 +9888,19 @@
         <v>660</v>
       </c>
       <c r="B321" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C321" t="s">
         <v>661</v>
       </c>
       <c r="D321" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E321" t="s">
         <v>10</v>
       </c>
       <c r="F321">
-        <v>207</v>
+        <v>283</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -9944,19 +9908,19 @@
         <v>662</v>
       </c>
       <c r="B322" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C322" t="s">
         <v>663</v>
       </c>
       <c r="D322" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E322" t="s">
         <v>10</v>
       </c>
       <c r="F322">
-        <v>141</v>
+        <v>216</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -9964,19 +9928,19 @@
         <v>664</v>
       </c>
       <c r="B323" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C323" t="s">
         <v>665</v>
       </c>
       <c r="D323" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E323" t="s">
         <v>10</v>
       </c>
       <c r="F323">
-        <v>291</v>
+        <v>155</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -9984,19 +9948,19 @@
         <v>666</v>
       </c>
       <c r="B324" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C324" t="s">
         <v>667</v>
       </c>
       <c r="D324" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E324" t="s">
         <v>10</v>
       </c>
       <c r="F324">
-        <v>242</v>
+        <v>158</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -10004,19 +9968,19 @@
         <v>668</v>
       </c>
       <c r="B325" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C325" t="s">
         <v>669</v>
       </c>
       <c r="D325" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E325" t="s">
         <v>10</v>
       </c>
       <c r="F325">
-        <v>245</v>
+        <v>297</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -10024,19 +9988,19 @@
         <v>670</v>
       </c>
       <c r="B326" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C326" t="s">
         <v>671</v>
       </c>
       <c r="D326" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E326" t="s">
         <v>10</v>
       </c>
       <c r="F326">
-        <v>225</v>
+        <v>148</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -10044,19 +10008,19 @@
         <v>672</v>
       </c>
       <c r="B327" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C327" t="s">
         <v>673</v>
       </c>
       <c r="D327" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E327" t="s">
         <v>10</v>
       </c>
       <c r="F327">
-        <v>166</v>
+        <v>154</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -10064,19 +10028,19 @@
         <v>674</v>
       </c>
       <c r="B328" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C328" t="s">
         <v>675</v>
       </c>
       <c r="D328" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E328" t="s">
         <v>10</v>
       </c>
       <c r="F328">
-        <v>220</v>
+        <v>160</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -10084,19 +10048,19 @@
         <v>676</v>
       </c>
       <c r="B329" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C329" t="s">
         <v>677</v>
       </c>
       <c r="D329" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E329" t="s">
         <v>10</v>
       </c>
       <c r="F329">
-        <v>102</v>
+        <v>146</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -10104,19 +10068,19 @@
         <v>678</v>
       </c>
       <c r="B330" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C330" t="s">
         <v>679</v>
       </c>
       <c r="D330" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E330" t="s">
         <v>10</v>
       </c>
       <c r="F330">
-        <v>199</v>
+        <v>252</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -10124,19 +10088,19 @@
         <v>680</v>
       </c>
       <c r="B331" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C331" t="s">
         <v>681</v>
       </c>
       <c r="D331" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E331" t="s">
         <v>10</v>
       </c>
       <c r="F331">
-        <v>151</v>
+        <v>198</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -10144,19 +10108,19 @@
         <v>682</v>
       </c>
       <c r="B332" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C332" t="s">
         <v>683</v>
       </c>
       <c r="D332" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E332" t="s">
         <v>10</v>
       </c>
       <c r="F332">
-        <v>280</v>
+        <v>294</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -10164,19 +10128,19 @@
         <v>684</v>
       </c>
       <c r="B333" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C333" t="s">
         <v>685</v>
       </c>
       <c r="D333" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E333" t="s">
         <v>10</v>
       </c>
       <c r="F333">
-        <v>270</v>
+        <v>287</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -10184,39 +10148,39 @@
         <v>686</v>
       </c>
       <c r="B334" t="s">
-        <v>648</v>
+        <v>687</v>
       </c>
       <c r="C334" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D334" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E334" t="s">
         <v>10</v>
       </c>
       <c r="F334">
-        <v>184</v>
+        <v>233</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B335" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C335" t="s">
         <v>690</v>
       </c>
       <c r="D335" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E335" t="s">
         <v>10</v>
       </c>
       <c r="F335">
-        <v>230</v>
+        <v>203</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -10224,19 +10188,19 @@
         <v>691</v>
       </c>
       <c r="B336" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C336" t="s">
         <v>692</v>
       </c>
       <c r="D336" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E336" t="s">
         <v>10</v>
       </c>
       <c r="F336">
-        <v>247</v>
+        <v>106</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -10244,19 +10208,19 @@
         <v>693</v>
       </c>
       <c r="B337" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C337" t="s">
         <v>694</v>
       </c>
       <c r="D337" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E337" t="s">
         <v>10</v>
       </c>
       <c r="F337">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -10264,19 +10228,19 @@
         <v>695</v>
       </c>
       <c r="B338" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C338" t="s">
         <v>696</v>
       </c>
       <c r="D338" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E338" t="s">
         <v>10</v>
       </c>
       <c r="F338">
-        <v>153</v>
+        <v>238</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -10284,19 +10248,19 @@
         <v>697</v>
       </c>
       <c r="B339" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C339" t="s">
         <v>698</v>
       </c>
       <c r="D339" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E339" t="s">
         <v>10</v>
       </c>
       <c r="F339">
-        <v>106</v>
+        <v>123</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -10304,19 +10268,19 @@
         <v>699</v>
       </c>
       <c r="B340" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C340" t="s">
         <v>700</v>
       </c>
       <c r="D340" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E340" t="s">
         <v>10</v>
       </c>
       <c r="F340">
-        <v>114</v>
+        <v>148</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -10324,19 +10288,19 @@
         <v>701</v>
       </c>
       <c r="B341" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C341" t="s">
         <v>702</v>
       </c>
       <c r="D341" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E341" t="s">
         <v>10</v>
       </c>
       <c r="F341">
-        <v>215</v>
+        <v>133</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -10344,19 +10308,19 @@
         <v>703</v>
       </c>
       <c r="B342" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C342" t="s">
         <v>704</v>
       </c>
       <c r="D342" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E342" t="s">
         <v>10</v>
       </c>
       <c r="F342">
-        <v>210</v>
+        <v>127</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -10364,19 +10328,19 @@
         <v>705</v>
       </c>
       <c r="B343" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C343" t="s">
         <v>706</v>
       </c>
       <c r="D343" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E343" t="s">
         <v>10</v>
       </c>
       <c r="F343">
-        <v>140</v>
+        <v>245</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -10384,19 +10348,19 @@
         <v>707</v>
       </c>
       <c r="B344" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C344" t="s">
         <v>708</v>
       </c>
       <c r="D344" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E344" t="s">
         <v>10</v>
       </c>
       <c r="F344">
-        <v>102</v>
+        <v>296</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -10404,19 +10368,19 @@
         <v>709</v>
       </c>
       <c r="B345" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C345" t="s">
         <v>710</v>
       </c>
       <c r="D345" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E345" t="s">
         <v>10</v>
       </c>
       <c r="F345">
-        <v>128</v>
+        <v>107</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -10424,19 +10388,19 @@
         <v>711</v>
       </c>
       <c r="B346" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C346" t="s">
         <v>712</v>
       </c>
       <c r="D346" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E346" t="s">
         <v>10</v>
       </c>
       <c r="F346">
-        <v>134</v>
+        <v>275</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -10444,19 +10408,19 @@
         <v>713</v>
       </c>
       <c r="B347" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C347" t="s">
         <v>714</v>
       </c>
       <c r="D347" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E347" t="s">
         <v>10</v>
       </c>
       <c r="F347">
-        <v>189</v>
+        <v>133</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -10464,13 +10428,13 @@
         <v>715</v>
       </c>
       <c r="B348" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C348" t="s">
         <v>716</v>
       </c>
       <c r="D348" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E348" t="s">
         <v>10</v>
@@ -10484,19 +10448,19 @@
         <v>717</v>
       </c>
       <c r="B349" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C349" t="s">
         <v>718</v>
       </c>
       <c r="D349" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E349" t="s">
         <v>10</v>
       </c>
       <c r="F349">
-        <v>146</v>
+        <v>244</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -10504,19 +10468,19 @@
         <v>719</v>
       </c>
       <c r="B350" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C350" t="s">
         <v>720</v>
       </c>
       <c r="D350" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E350" t="s">
         <v>10</v>
       </c>
       <c r="F350">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -10524,19 +10488,19 @@
         <v>721</v>
       </c>
       <c r="B351" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C351" t="s">
         <v>722</v>
       </c>
       <c r="D351" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E351" t="s">
         <v>10</v>
       </c>
       <c r="F351">
-        <v>157</v>
+        <v>212</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -10544,19 +10508,19 @@
         <v>723</v>
       </c>
       <c r="B352" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C352" t="s">
         <v>724</v>
       </c>
       <c r="D352" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E352" t="s">
         <v>10</v>
       </c>
       <c r="F352">
-        <v>200</v>
+        <v>153</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -10564,19 +10528,19 @@
         <v>725</v>
       </c>
       <c r="B353" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C353" t="s">
         <v>726</v>
       </c>
       <c r="D353" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E353" t="s">
         <v>10</v>
       </c>
       <c r="F353">
-        <v>172</v>
+        <v>120</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
@@ -10584,39 +10548,39 @@
         <v>727</v>
       </c>
       <c r="B354" t="s">
-        <v>689</v>
+        <v>728</v>
       </c>
       <c r="C354" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D354" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E354" t="s">
         <v>10</v>
       </c>
       <c r="F354">
-        <v>267</v>
+        <v>107</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B355" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C355" t="s">
         <v>731</v>
       </c>
       <c r="D355" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E355" t="s">
         <v>10</v>
       </c>
       <c r="F355">
-        <v>227</v>
+        <v>233</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
@@ -10624,19 +10588,19 @@
         <v>732</v>
       </c>
       <c r="B356" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C356" t="s">
         <v>733</v>
       </c>
       <c r="D356" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E356" t="s">
         <v>10</v>
       </c>
       <c r="F356">
-        <v>209</v>
+        <v>153</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
@@ -10644,19 +10608,19 @@
         <v>734</v>
       </c>
       <c r="B357" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C357" t="s">
         <v>735</v>
       </c>
       <c r="D357" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E357" t="s">
         <v>10</v>
       </c>
       <c r="F357">
-        <v>157</v>
+        <v>131</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
@@ -10664,19 +10628,19 @@
         <v>736</v>
       </c>
       <c r="B358" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C358" t="s">
         <v>737</v>
       </c>
       <c r="D358" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E358" t="s">
         <v>10</v>
       </c>
       <c r="F358">
-        <v>182</v>
+        <v>139</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
@@ -10684,19 +10648,19 @@
         <v>738</v>
       </c>
       <c r="B359" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C359" t="s">
         <v>739</v>
       </c>
       <c r="D359" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E359" t="s">
         <v>10</v>
       </c>
       <c r="F359">
-        <v>215</v>
+        <v>117</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -10704,19 +10668,19 @@
         <v>740</v>
       </c>
       <c r="B360" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C360" t="s">
         <v>741</v>
       </c>
       <c r="D360" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E360" t="s">
         <v>10</v>
       </c>
       <c r="F360">
-        <v>260</v>
+        <v>217</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -10724,19 +10688,19 @@
         <v>742</v>
       </c>
       <c r="B361" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C361" t="s">
         <v>743</v>
       </c>
       <c r="D361" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E361" t="s">
         <v>10</v>
       </c>
       <c r="F361">
-        <v>188</v>
+        <v>215</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -10744,19 +10708,19 @@
         <v>744</v>
       </c>
       <c r="B362" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C362" t="s">
         <v>745</v>
       </c>
       <c r="D362" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E362" t="s">
         <v>10</v>
       </c>
       <c r="F362">
-        <v>165</v>
+        <v>234</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -10764,19 +10728,19 @@
         <v>746</v>
       </c>
       <c r="B363" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C363" t="s">
         <v>747</v>
       </c>
       <c r="D363" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E363" t="s">
         <v>10</v>
       </c>
       <c r="F363">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -10784,19 +10748,19 @@
         <v>748</v>
       </c>
       <c r="B364" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C364" t="s">
         <v>749</v>
       </c>
       <c r="D364" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E364" t="s">
         <v>10</v>
       </c>
       <c r="F364">
-        <v>244</v>
+        <v>205</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -10804,19 +10768,19 @@
         <v>750</v>
       </c>
       <c r="B365" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C365" t="s">
         <v>751</v>
       </c>
       <c r="D365" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E365" t="s">
         <v>10</v>
       </c>
       <c r="F365">
-        <v>263</v>
+        <v>118</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -10824,19 +10788,19 @@
         <v>752</v>
       </c>
       <c r="B366" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C366" t="s">
         <v>753</v>
       </c>
       <c r="D366" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E366" t="s">
         <v>10</v>
       </c>
       <c r="F366">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -10844,19 +10808,19 @@
         <v>754</v>
       </c>
       <c r="B367" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C367" t="s">
         <v>755</v>
       </c>
       <c r="D367" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E367" t="s">
         <v>10</v>
       </c>
       <c r="F367">
-        <v>165</v>
+        <v>135</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -10864,19 +10828,19 @@
         <v>756</v>
       </c>
       <c r="B368" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C368" t="s">
         <v>757</v>
       </c>
       <c r="D368" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E368" t="s">
         <v>10</v>
       </c>
       <c r="F368">
-        <v>148</v>
+        <v>217</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -10884,19 +10848,19 @@
         <v>758</v>
       </c>
       <c r="B369" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C369" t="s">
         <v>759</v>
       </c>
       <c r="D369" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E369" t="s">
         <v>10</v>
       </c>
       <c r="F369">
-        <v>126</v>
+        <v>107</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -10904,19 +10868,19 @@
         <v>760</v>
       </c>
       <c r="B370" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C370" t="s">
         <v>761</v>
       </c>
       <c r="D370" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E370" t="s">
         <v>10</v>
       </c>
       <c r="F370">
-        <v>293</v>
+        <v>141</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -10924,19 +10888,19 @@
         <v>762</v>
       </c>
       <c r="B371" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C371" t="s">
         <v>763</v>
       </c>
       <c r="D371" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E371" t="s">
         <v>10</v>
       </c>
       <c r="F371">
-        <v>241</v>
+        <v>137</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -10944,19 +10908,19 @@
         <v>764</v>
       </c>
       <c r="B372" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C372" t="s">
         <v>765</v>
       </c>
       <c r="D372" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E372" t="s">
         <v>10</v>
       </c>
       <c r="F372">
-        <v>275</v>
+        <v>249</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -10964,19 +10928,19 @@
         <v>766</v>
       </c>
       <c r="B373" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C373" t="s">
         <v>767</v>
       </c>
       <c r="D373" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E373" t="s">
         <v>10</v>
       </c>
       <c r="F373">
-        <v>287</v>
+        <v>150</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
@@ -10984,39 +10948,39 @@
         <v>768</v>
       </c>
       <c r="B374" t="s">
-        <v>730</v>
+        <v>769</v>
       </c>
       <c r="C374" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D374" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E374" t="s">
         <v>10</v>
       </c>
       <c r="F374">
-        <v>148</v>
+        <v>113</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B375" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C375" t="s">
         <v>772</v>
       </c>
       <c r="D375" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E375" t="s">
         <v>10</v>
       </c>
       <c r="F375">
-        <v>159</v>
+        <v>186</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -11024,19 +10988,19 @@
         <v>773</v>
       </c>
       <c r="B376" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C376" t="s">
         <v>774</v>
       </c>
       <c r="D376" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E376" t="s">
         <v>10</v>
       </c>
       <c r="F376">
-        <v>209</v>
+        <v>194</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -11044,19 +11008,19 @@
         <v>775</v>
       </c>
       <c r="B377" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C377" t="s">
         <v>776</v>
       </c>
       <c r="D377" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E377" t="s">
         <v>10</v>
       </c>
       <c r="F377">
-        <v>103</v>
+        <v>164</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -11064,19 +11028,19 @@
         <v>777</v>
       </c>
       <c r="B378" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C378" t="s">
         <v>778</v>
       </c>
       <c r="D378" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E378" t="s">
         <v>10</v>
       </c>
       <c r="F378">
-        <v>115</v>
+        <v>265</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -11084,19 +11048,19 @@
         <v>779</v>
       </c>
       <c r="B379" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C379" t="s">
         <v>780</v>
       </c>
       <c r="D379" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E379" t="s">
         <v>10</v>
       </c>
       <c r="F379">
-        <v>216</v>
+        <v>285</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -11104,19 +11068,19 @@
         <v>781</v>
       </c>
       <c r="B380" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C380" t="s">
         <v>782</v>
       </c>
       <c r="D380" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E380" t="s">
         <v>10</v>
       </c>
       <c r="F380">
-        <v>198</v>
+        <v>110</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -11124,19 +11088,19 @@
         <v>783</v>
       </c>
       <c r="B381" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C381" t="s">
         <v>784</v>
       </c>
       <c r="D381" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E381" t="s">
         <v>10</v>
       </c>
       <c r="F381">
-        <v>103</v>
+        <v>187</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -11144,19 +11108,19 @@
         <v>785</v>
       </c>
       <c r="B382" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C382" t="s">
         <v>786</v>
       </c>
       <c r="D382" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E382" t="s">
         <v>10</v>
       </c>
       <c r="F382">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -11164,19 +11128,19 @@
         <v>787</v>
       </c>
       <c r="B383" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C383" t="s">
         <v>788</v>
       </c>
       <c r="D383" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E383" t="s">
         <v>10</v>
       </c>
       <c r="F383">
-        <v>128</v>
+        <v>294</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -11184,19 +11148,19 @@
         <v>789</v>
       </c>
       <c r="B384" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C384" t="s">
         <v>790</v>
       </c>
       <c r="D384" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E384" t="s">
         <v>10</v>
       </c>
       <c r="F384">
-        <v>174</v>
+        <v>294</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -11204,19 +11168,19 @@
         <v>791</v>
       </c>
       <c r="B385" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C385" t="s">
         <v>792</v>
       </c>
       <c r="D385" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E385" t="s">
         <v>10</v>
       </c>
       <c r="F385">
-        <v>179</v>
+        <v>142</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -11224,19 +11188,19 @@
         <v>793</v>
       </c>
       <c r="B386" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C386" t="s">
         <v>794</v>
       </c>
       <c r="D386" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E386" t="s">
         <v>10</v>
       </c>
       <c r="F386">
-        <v>201</v>
+        <v>295</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -11244,13 +11208,13 @@
         <v>795</v>
       </c>
       <c r="B387" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C387" t="s">
         <v>796</v>
       </c>
       <c r="D387" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E387" t="s">
         <v>10</v>
@@ -11264,19 +11228,19 @@
         <v>797</v>
       </c>
       <c r="B388" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C388" t="s">
         <v>798</v>
       </c>
       <c r="D388" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E388" t="s">
         <v>10</v>
       </c>
       <c r="F388">
-        <v>168</v>
+        <v>113</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -11284,19 +11248,19 @@
         <v>799</v>
       </c>
       <c r="B389" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C389" t="s">
         <v>800</v>
       </c>
       <c r="D389" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E389" t="s">
         <v>10</v>
       </c>
       <c r="F389">
-        <v>158</v>
+        <v>249</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -11304,19 +11268,19 @@
         <v>801</v>
       </c>
       <c r="B390" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C390" t="s">
         <v>802</v>
       </c>
       <c r="D390" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E390" t="s">
         <v>10</v>
       </c>
       <c r="F390">
-        <v>147</v>
+        <v>213</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -11324,19 +11288,19 @@
         <v>803</v>
       </c>
       <c r="B391" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C391" t="s">
         <v>804</v>
       </c>
       <c r="D391" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E391" t="s">
         <v>10</v>
       </c>
       <c r="F391">
-        <v>173</v>
+        <v>286</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -11344,19 +11308,19 @@
         <v>805</v>
       </c>
       <c r="B392" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C392" t="s">
         <v>806</v>
       </c>
       <c r="D392" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E392" t="s">
         <v>10</v>
       </c>
       <c r="F392">
-        <v>270</v>
+        <v>175</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -11364,19 +11328,19 @@
         <v>807</v>
       </c>
       <c r="B393" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C393" t="s">
         <v>808</v>
       </c>
       <c r="D393" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E393" t="s">
         <v>10</v>
       </c>
       <c r="F393">
-        <v>145</v>
+        <v>117</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -11384,39 +11348,39 @@
         <v>809</v>
       </c>
       <c r="B394" t="s">
-        <v>771</v>
+        <v>810</v>
       </c>
       <c r="C394" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D394" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E394" t="s">
         <v>10</v>
       </c>
       <c r="F394">
-        <v>290</v>
+        <v>205</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B395" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C395" t="s">
         <v>813</v>
       </c>
       <c r="D395" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E395" t="s">
         <v>10</v>
       </c>
       <c r="F395">
-        <v>198</v>
+        <v>118</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -11424,19 +11388,19 @@
         <v>814</v>
       </c>
       <c r="B396" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C396" t="s">
         <v>815</v>
       </c>
       <c r="D396" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E396" t="s">
         <v>10</v>
       </c>
       <c r="F396">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -11444,19 +11408,19 @@
         <v>816</v>
       </c>
       <c r="B397" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C397" t="s">
         <v>817</v>
       </c>
       <c r="D397" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E397" t="s">
         <v>10</v>
       </c>
       <c r="F397">
-        <v>285</v>
+        <v>163</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -11464,19 +11428,19 @@
         <v>818</v>
       </c>
       <c r="B398" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C398" t="s">
         <v>819</v>
       </c>
       <c r="D398" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E398" t="s">
         <v>10</v>
       </c>
       <c r="F398">
-        <v>289</v>
+        <v>224</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -11484,19 +11448,19 @@
         <v>820</v>
       </c>
       <c r="B399" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C399" t="s">
         <v>821</v>
       </c>
       <c r="D399" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E399" t="s">
         <v>10</v>
       </c>
       <c r="F399">
-        <v>258</v>
+        <v>182</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -11504,19 +11468,19 @@
         <v>822</v>
       </c>
       <c r="B400" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C400" t="s">
         <v>823</v>
       </c>
       <c r="D400" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E400" t="s">
         <v>10</v>
       </c>
       <c r="F400">
-        <v>277</v>
+        <v>235</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -11524,19 +11488,19 @@
         <v>824</v>
       </c>
       <c r="B401" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C401" t="s">
         <v>825</v>
       </c>
       <c r="D401" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E401" t="s">
         <v>10</v>
       </c>
       <c r="F401">
-        <v>225</v>
+        <v>202</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
@@ -11544,19 +11508,19 @@
         <v>826</v>
       </c>
       <c r="B402" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C402" t="s">
         <v>827</v>
       </c>
       <c r="D402" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E402" t="s">
         <v>10</v>
       </c>
       <c r="F402">
-        <v>255</v>
+        <v>285</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -11564,19 +11528,19 @@
         <v>828</v>
       </c>
       <c r="B403" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C403" t="s">
         <v>829</v>
       </c>
       <c r="D403" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E403" t="s">
         <v>10</v>
       </c>
       <c r="F403">
-        <v>258</v>
+        <v>172</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -11584,10 +11548,10 @@
         <v>830</v>
       </c>
       <c r="B404" t="s">
-        <v>812</v>
+        <v>831</v>
       </c>
       <c r="C404" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D404" t="s">
         <v>9</v>
@@ -11596,27 +11560,27 @@
         <v>10</v>
       </c>
       <c r="F404">
-        <v>294</v>
+        <v>151</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B405" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C405" t="s">
         <v>834</v>
       </c>
       <c r="D405" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E405" t="s">
         <v>10</v>
       </c>
       <c r="F405">
-        <v>255</v>
+        <v>246</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -11624,19 +11588,19 @@
         <v>835</v>
       </c>
       <c r="B406" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C406" t="s">
         <v>836</v>
       </c>
       <c r="D406" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E406" t="s">
         <v>10</v>
       </c>
       <c r="F406">
-        <v>297</v>
+        <v>239</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -11644,19 +11608,19 @@
         <v>837</v>
       </c>
       <c r="B407" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C407" t="s">
         <v>838</v>
       </c>
       <c r="D407" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E407" t="s">
         <v>10</v>
       </c>
       <c r="F407">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
@@ -11664,19 +11628,19 @@
         <v>839</v>
       </c>
       <c r="B408" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C408" t="s">
         <v>840</v>
       </c>
       <c r="D408" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E408" t="s">
         <v>10</v>
       </c>
       <c r="F408">
-        <v>185</v>
+        <v>271</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -11684,19 +11648,19 @@
         <v>841</v>
       </c>
       <c r="B409" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C409" t="s">
         <v>842</v>
       </c>
       <c r="D409" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E409" t="s">
         <v>10</v>
       </c>
       <c r="F409">
-        <v>102</v>
+        <v>227</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -11704,19 +11668,19 @@
         <v>843</v>
       </c>
       <c r="B410" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C410" t="s">
         <v>844</v>
       </c>
       <c r="D410" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E410" t="s">
         <v>10</v>
       </c>
       <c r="F410">
-        <v>168</v>
+        <v>106</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
@@ -11724,19 +11688,19 @@
         <v>845</v>
       </c>
       <c r="B411" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C411" t="s">
         <v>846</v>
       </c>
       <c r="D411" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E411" t="s">
         <v>10</v>
       </c>
       <c r="F411">
-        <v>100</v>
+        <v>273</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
@@ -11744,19 +11708,19 @@
         <v>847</v>
       </c>
       <c r="B412" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C412" t="s">
         <v>848</v>
       </c>
       <c r="D412" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E412" t="s">
         <v>10</v>
       </c>
       <c r="F412">
-        <v>233</v>
+        <v>195</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
@@ -11764,19 +11728,19 @@
         <v>849</v>
       </c>
       <c r="B413" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C413" t="s">
         <v>850</v>
       </c>
       <c r="D413" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E413" t="s">
         <v>10</v>
       </c>
       <c r="F413">
-        <v>201</v>
+        <v>216</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
@@ -11784,19 +11748,19 @@
         <v>851</v>
       </c>
       <c r="B414" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C414" t="s">
         <v>852</v>
       </c>
       <c r="D414" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E414" t="s">
         <v>10</v>
       </c>
       <c r="F414">
-        <v>234</v>
+        <v>267</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
@@ -11804,19 +11768,19 @@
         <v>853</v>
       </c>
       <c r="B415" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C415" t="s">
         <v>854</v>
       </c>
       <c r="D415" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E415" t="s">
         <v>10</v>
       </c>
       <c r="F415">
-        <v>159</v>
+        <v>243</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
@@ -11824,19 +11788,19 @@
         <v>855</v>
       </c>
       <c r="B416" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C416" t="s">
         <v>856</v>
       </c>
       <c r="D416" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E416" t="s">
         <v>10</v>
       </c>
       <c r="F416">
-        <v>178</v>
+        <v>296</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
@@ -11844,19 +11808,19 @@
         <v>857</v>
       </c>
       <c r="B417" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C417" t="s">
         <v>858</v>
       </c>
       <c r="D417" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E417" t="s">
         <v>10</v>
       </c>
       <c r="F417">
-        <v>102</v>
+        <v>283</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
@@ -11864,19 +11828,19 @@
         <v>859</v>
       </c>
       <c r="B418" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C418" t="s">
         <v>860</v>
       </c>
       <c r="D418" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E418" t="s">
         <v>10</v>
       </c>
       <c r="F418">
-        <v>191</v>
+        <v>246</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
@@ -11884,19 +11848,19 @@
         <v>861</v>
       </c>
       <c r="B419" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C419" t="s">
         <v>862</v>
       </c>
       <c r="D419" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E419" t="s">
         <v>10</v>
       </c>
       <c r="F419">
-        <v>251</v>
+        <v>132</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
@@ -11904,19 +11868,19 @@
         <v>863</v>
       </c>
       <c r="B420" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C420" t="s">
         <v>864</v>
       </c>
       <c r="D420" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E420" t="s">
         <v>10</v>
       </c>
       <c r="F420">
-        <v>249</v>
+        <v>192</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -11924,19 +11888,19 @@
         <v>865</v>
       </c>
       <c r="B421" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C421" t="s">
         <v>866</v>
       </c>
       <c r="D421" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E421" t="s">
         <v>10</v>
       </c>
       <c r="F421">
-        <v>121</v>
+        <v>156</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
@@ -11944,19 +11908,19 @@
         <v>867</v>
       </c>
       <c r="B422" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C422" t="s">
         <v>868</v>
       </c>
       <c r="D422" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E422" t="s">
         <v>10</v>
       </c>
       <c r="F422">
-        <v>231</v>
+        <v>213</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
@@ -11964,10 +11928,10 @@
         <v>869</v>
       </c>
       <c r="B423" t="s">
-        <v>833</v>
+        <v>870</v>
       </c>
       <c r="C423" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D423" t="s">
         <v>9</v>
@@ -11976,18 +11940,18 @@
         <v>10</v>
       </c>
       <c r="F423">
-        <v>195</v>
+        <v>140</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B424" t="s">
-        <v>833</v>
+        <v>870</v>
       </c>
       <c r="C424" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D424" t="s">
         <v>13</v>
@@ -11996,27 +11960,27 @@
         <v>10</v>
       </c>
       <c r="F424">
-        <v>261</v>
+        <v>287</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B425" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C425" t="s">
         <v>875</v>
       </c>
       <c r="D425" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E425" t="s">
         <v>10</v>
       </c>
       <c r="F425">
-        <v>197</v>
+        <v>284</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -12024,19 +11988,19 @@
         <v>876</v>
       </c>
       <c r="B426" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C426" t="s">
         <v>877</v>
       </c>
       <c r="D426" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E426" t="s">
         <v>10</v>
       </c>
       <c r="F426">
-        <v>231</v>
+        <v>299</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -12044,19 +12008,19 @@
         <v>878</v>
       </c>
       <c r="B427" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C427" t="s">
         <v>879</v>
       </c>
       <c r="D427" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E427" t="s">
         <v>10</v>
       </c>
       <c r="F427">
-        <v>101</v>
+        <v>286</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
@@ -12064,19 +12028,19 @@
         <v>880</v>
       </c>
       <c r="B428" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C428" t="s">
         <v>881</v>
       </c>
       <c r="D428" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E428" t="s">
         <v>10</v>
       </c>
       <c r="F428">
-        <v>113</v>
+        <v>227</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -12084,19 +12048,19 @@
         <v>882</v>
       </c>
       <c r="B429" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C429" t="s">
         <v>883</v>
       </c>
       <c r="D429" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E429" t="s">
         <v>10</v>
       </c>
       <c r="F429">
-        <v>147</v>
+        <v>206</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -12104,19 +12068,19 @@
         <v>884</v>
       </c>
       <c r="B430" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C430" t="s">
         <v>885</v>
       </c>
       <c r="D430" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E430" t="s">
         <v>10</v>
       </c>
       <c r="F430">
-        <v>287</v>
+        <v>138</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -12124,19 +12088,19 @@
         <v>886</v>
       </c>
       <c r="B431" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C431" t="s">
         <v>887</v>
       </c>
       <c r="D431" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E431" t="s">
         <v>10</v>
       </c>
       <c r="F431">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -12144,19 +12108,19 @@
         <v>888</v>
       </c>
       <c r="B432" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C432" t="s">
         <v>889</v>
       </c>
       <c r="D432" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E432" t="s">
         <v>10</v>
       </c>
       <c r="F432">
-        <v>236</v>
+        <v>132</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -12164,59 +12128,59 @@
         <v>890</v>
       </c>
       <c r="B433" t="s">
-        <v>874</v>
+        <v>891</v>
       </c>
       <c r="C433" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D433" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E433" t="s">
         <v>10</v>
       </c>
       <c r="F433">
-        <v>287</v>
+        <v>169</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B434" t="s">
-        <v>874</v>
+        <v>891</v>
       </c>
       <c r="C434" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D434" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E434" t="s">
         <v>10</v>
       </c>
       <c r="F434">
-        <v>125</v>
+        <v>173</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B435" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="C435" t="s">
         <v>896</v>
       </c>
       <c r="D435" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E435" t="s">
         <v>10</v>
       </c>
       <c r="F435">
-        <v>223</v>
+        <v>289</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
@@ -12224,19 +12188,19 @@
         <v>897</v>
       </c>
       <c r="B436" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="C436" t="s">
         <v>898</v>
       </c>
       <c r="D436" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E436" t="s">
         <v>10</v>
       </c>
       <c r="F436">
-        <v>226</v>
+        <v>131</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -12244,19 +12208,19 @@
         <v>899</v>
       </c>
       <c r="B437" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="C437" t="s">
         <v>900</v>
       </c>
       <c r="D437" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E437" t="s">
         <v>10</v>
       </c>
       <c r="F437">
-        <v>144</v>
+        <v>223</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -12264,19 +12228,19 @@
         <v>901</v>
       </c>
       <c r="B438" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="C438" t="s">
         <v>902</v>
       </c>
       <c r="D438" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E438" t="s">
         <v>10</v>
       </c>
       <c r="F438">
-        <v>110</v>
+        <v>157</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -12284,19 +12248,19 @@
         <v>903</v>
       </c>
       <c r="B439" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="C439" t="s">
         <v>904</v>
       </c>
       <c r="D439" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E439" t="s">
         <v>10</v>
       </c>
       <c r="F439">
-        <v>241</v>
+        <v>264</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -12304,19 +12268,19 @@
         <v>905</v>
       </c>
       <c r="B440" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="C440" t="s">
         <v>906</v>
       </c>
       <c r="D440" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E440" t="s">
         <v>10</v>
       </c>
       <c r="F440">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -12324,19 +12288,19 @@
         <v>907</v>
       </c>
       <c r="B441" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="C441" t="s">
         <v>908</v>
       </c>
       <c r="D441" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E441" t="s">
         <v>10</v>
       </c>
       <c r="F441">
-        <v>168</v>
+        <v>118</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -12344,19 +12308,19 @@
         <v>909</v>
       </c>
       <c r="B442" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="C442" t="s">
         <v>910</v>
       </c>
       <c r="D442" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E442" t="s">
         <v>10</v>
       </c>
       <c r="F442">
-        <v>297</v>
+        <v>128</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
@@ -12364,19 +12328,19 @@
         <v>911</v>
       </c>
       <c r="B443" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="C443" t="s">
         <v>912</v>
       </c>
       <c r="D443" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E443" t="s">
         <v>10</v>
       </c>
       <c r="F443">
-        <v>109</v>
+        <v>213</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -12384,19 +12348,19 @@
         <v>913</v>
       </c>
       <c r="B444" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="C444" t="s">
         <v>914</v>
       </c>
       <c r="D444" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E444" t="s">
         <v>10</v>
       </c>
       <c r="F444">
-        <v>214</v>
+        <v>142</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
@@ -12404,19 +12368,19 @@
         <v>915</v>
       </c>
       <c r="B445" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="C445" t="s">
         <v>916</v>
       </c>
       <c r="D445" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E445" t="s">
         <v>10</v>
       </c>
       <c r="F445">
-        <v>115</v>
+        <v>179</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -12424,19 +12388,19 @@
         <v>917</v>
       </c>
       <c r="B446" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="C446" t="s">
         <v>918</v>
       </c>
       <c r="D446" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E446" t="s">
         <v>10</v>
       </c>
       <c r="F446">
-        <v>272</v>
+        <v>251</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -12444,19 +12408,19 @@
         <v>919</v>
       </c>
       <c r="B447" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="C447" t="s">
         <v>920</v>
       </c>
       <c r="D447" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E447" t="s">
         <v>10</v>
       </c>
       <c r="F447">
-        <v>287</v>
+        <v>113</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
@@ -12464,7 +12428,7 @@
         <v>921</v>
       </c>
       <c r="B448" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="C448" t="s">
         <v>922</v>
@@ -12476,7 +12440,7 @@
         <v>10</v>
       </c>
       <c r="F448">
-        <v>280</v>
+        <v>251</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
@@ -12484,7 +12448,7 @@
         <v>923</v>
       </c>
       <c r="B449" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="C449" t="s">
         <v>924</v>
@@ -12496,7 +12460,7 @@
         <v>10</v>
       </c>
       <c r="F449">
-        <v>220</v>
+        <v>207</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
@@ -12504,7 +12468,7 @@
         <v>925</v>
       </c>
       <c r="B450" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="C450" t="s">
         <v>926</v>
@@ -12516,7 +12480,7 @@
         <v>10</v>
       </c>
       <c r="F450">
-        <v>259</v>
+        <v>299</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
@@ -12524,7 +12488,7 @@
         <v>927</v>
       </c>
       <c r="B451" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="C451" t="s">
         <v>928</v>
@@ -12536,7 +12500,7 @@
         <v>10</v>
       </c>
       <c r="F451">
-        <v>122</v>
+        <v>164</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
@@ -12544,67 +12508,67 @@
         <v>929</v>
       </c>
       <c r="B452" t="s">
-        <v>895</v>
+        <v>930</v>
       </c>
       <c r="C452" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="D452" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E452" t="s">
         <v>10</v>
       </c>
       <c r="F452">
-        <v>275</v>
+        <v>121</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B453" t="s">
-        <v>895</v>
+        <v>930</v>
       </c>
       <c r="C453" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D453" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E453" t="s">
         <v>10</v>
       </c>
       <c r="F453">
-        <v>275</v>
+        <v>244</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B454" t="s">
-        <v>895</v>
+        <v>930</v>
       </c>
       <c r="C454" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D454" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E454" t="s">
         <v>10</v>
       </c>
       <c r="F454">
-        <v>290</v>
+        <v>146</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B455" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C455" t="s">
         <v>937</v>
@@ -12616,7 +12580,7 @@
         <v>10</v>
       </c>
       <c r="F455">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
@@ -12624,7 +12588,7 @@
         <v>938</v>
       </c>
       <c r="B456" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C456" t="s">
         <v>939</v>
@@ -12636,7 +12600,7 @@
         <v>10</v>
       </c>
       <c r="F456">
-        <v>166</v>
+        <v>293</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
@@ -12644,7 +12608,7 @@
         <v>940</v>
       </c>
       <c r="B457" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C457" t="s">
         <v>941</v>
@@ -12656,7 +12620,7 @@
         <v>10</v>
       </c>
       <c r="F457">
-        <v>277</v>
+        <v>243</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
@@ -12664,7 +12628,7 @@
         <v>942</v>
       </c>
       <c r="B458" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C458" t="s">
         <v>943</v>
@@ -12676,7 +12640,7 @@
         <v>10</v>
       </c>
       <c r="F458">
-        <v>182</v>
+        <v>270</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
@@ -12684,7 +12648,7 @@
         <v>944</v>
       </c>
       <c r="B459" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C459" t="s">
         <v>945</v>
@@ -12696,7 +12660,7 @@
         <v>10</v>
       </c>
       <c r="F459">
-        <v>240</v>
+        <v>140</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
@@ -12704,7 +12668,7 @@
         <v>946</v>
       </c>
       <c r="B460" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C460" t="s">
         <v>947</v>
@@ -12716,7 +12680,7 @@
         <v>10</v>
       </c>
       <c r="F460">
-        <v>203</v>
+        <v>268</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
@@ -12724,7 +12688,7 @@
         <v>948</v>
       </c>
       <c r="B461" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C461" t="s">
         <v>949</v>
@@ -12736,7 +12700,7 @@
         <v>10</v>
       </c>
       <c r="F461">
-        <v>242</v>
+        <v>256</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
@@ -12744,7 +12708,7 @@
         <v>950</v>
       </c>
       <c r="B462" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C462" t="s">
         <v>951</v>
@@ -12756,7 +12720,7 @@
         <v>10</v>
       </c>
       <c r="F462">
-        <v>204</v>
+        <v>185</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
@@ -12764,7 +12728,7 @@
         <v>952</v>
       </c>
       <c r="B463" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C463" t="s">
         <v>953</v>
@@ -12776,7 +12740,7 @@
         <v>10</v>
       </c>
       <c r="F463">
-        <v>167</v>
+        <v>111</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
@@ -12784,7 +12748,7 @@
         <v>954</v>
       </c>
       <c r="B464" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C464" t="s">
         <v>955</v>
@@ -12796,7 +12760,7 @@
         <v>10</v>
       </c>
       <c r="F464">
-        <v>165</v>
+        <v>224</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
@@ -12804,7 +12768,7 @@
         <v>956</v>
       </c>
       <c r="B465" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C465" t="s">
         <v>957</v>
@@ -12816,7 +12780,7 @@
         <v>10</v>
       </c>
       <c r="F465">
-        <v>146</v>
+        <v>115</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
@@ -12824,7 +12788,7 @@
         <v>958</v>
       </c>
       <c r="B466" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C466" t="s">
         <v>959</v>
@@ -12836,7 +12800,7 @@
         <v>10</v>
       </c>
       <c r="F466">
-        <v>189</v>
+        <v>138</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
@@ -12844,7 +12808,7 @@
         <v>960</v>
       </c>
       <c r="B467" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C467" t="s">
         <v>961</v>
@@ -12856,7 +12820,7 @@
         <v>10</v>
       </c>
       <c r="F467">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
@@ -12864,7 +12828,7 @@
         <v>962</v>
       </c>
       <c r="B468" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C468" t="s">
         <v>963</v>
@@ -12876,7 +12840,7 @@
         <v>10</v>
       </c>
       <c r="F468">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
@@ -12884,19 +12848,19 @@
         <v>964</v>
       </c>
       <c r="B469" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C469" t="s">
         <v>965</v>
       </c>
       <c r="D469" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E469" t="s">
         <v>10</v>
       </c>
       <c r="F469">
-        <v>107</v>
+        <v>136</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
@@ -12904,19 +12868,19 @@
         <v>966</v>
       </c>
       <c r="B470" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C470" t="s">
         <v>967</v>
       </c>
       <c r="D470" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E470" t="s">
         <v>10</v>
       </c>
       <c r="F470">
-        <v>125</v>
+        <v>268</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
@@ -12924,19 +12888,19 @@
         <v>968</v>
       </c>
       <c r="B471" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C471" t="s">
         <v>969</v>
       </c>
       <c r="D471" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E471" t="s">
         <v>10</v>
       </c>
       <c r="F471">
-        <v>154</v>
+        <v>279</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
@@ -12944,19 +12908,19 @@
         <v>970</v>
       </c>
       <c r="B472" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C472" t="s">
         <v>971</v>
       </c>
       <c r="D472" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E472" t="s">
         <v>10</v>
       </c>
       <c r="F472">
-        <v>118</v>
+        <v>153</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
@@ -12964,19 +12928,19 @@
         <v>972</v>
       </c>
       <c r="B473" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C473" t="s">
         <v>973</v>
       </c>
       <c r="D473" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E473" t="s">
         <v>10</v>
       </c>
       <c r="F473">
-        <v>241</v>
+        <v>275</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
@@ -12984,19 +12948,19 @@
         <v>974</v>
       </c>
       <c r="B474" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C474" t="s">
         <v>975</v>
       </c>
       <c r="D474" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E474" t="s">
         <v>10</v>
       </c>
       <c r="F474">
-        <v>237</v>
+        <v>182</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
@@ -13004,19 +12968,19 @@
         <v>976</v>
       </c>
       <c r="B475" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C475" t="s">
         <v>977</v>
       </c>
       <c r="D475" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E475" t="s">
         <v>10</v>
       </c>
       <c r="F475">
-        <v>153</v>
+        <v>204</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
@@ -13024,19 +12988,19 @@
         <v>978</v>
       </c>
       <c r="B476" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C476" t="s">
         <v>979</v>
       </c>
       <c r="D476" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E476" t="s">
         <v>10</v>
       </c>
       <c r="F476">
-        <v>203</v>
+        <v>246</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
@@ -13044,19 +13008,19 @@
         <v>980</v>
       </c>
       <c r="B477" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C477" t="s">
         <v>981</v>
       </c>
       <c r="D477" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E477" t="s">
         <v>10</v>
       </c>
       <c r="F477">
-        <v>142</v>
+        <v>159</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
@@ -13064,19 +13028,19 @@
         <v>982</v>
       </c>
       <c r="B478" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C478" t="s">
         <v>983</v>
       </c>
       <c r="D478" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E478" t="s">
         <v>10</v>
       </c>
       <c r="F478">
-        <v>246</v>
+        <v>258</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
@@ -13084,19 +13048,19 @@
         <v>984</v>
       </c>
       <c r="B479" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C479" t="s">
         <v>985</v>
       </c>
       <c r="D479" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E479" t="s">
         <v>10</v>
       </c>
       <c r="F479">
-        <v>206</v>
+        <v>278</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
@@ -13104,19 +13068,19 @@
         <v>986</v>
       </c>
       <c r="B480" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C480" t="s">
         <v>987</v>
       </c>
       <c r="D480" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E480" t="s">
         <v>10</v>
       </c>
       <c r="F480">
-        <v>200</v>
+        <v>173</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
@@ -13124,19 +13088,19 @@
         <v>988</v>
       </c>
       <c r="B481" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C481" t="s">
         <v>989</v>
       </c>
       <c r="D481" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E481" t="s">
         <v>10</v>
       </c>
       <c r="F481">
-        <v>117</v>
+        <v>260</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
@@ -13144,19 +13108,19 @@
         <v>990</v>
       </c>
       <c r="B482" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C482" t="s">
         <v>991</v>
       </c>
       <c r="D482" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E482" t="s">
         <v>10</v>
       </c>
       <c r="F482">
-        <v>263</v>
+        <v>104</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
@@ -13164,19 +13128,19 @@
         <v>992</v>
       </c>
       <c r="B483" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C483" t="s">
         <v>993</v>
       </c>
       <c r="D483" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E483" t="s">
         <v>10</v>
       </c>
       <c r="F483">
-        <v>150</v>
+        <v>235</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
@@ -13184,19 +13148,19 @@
         <v>994</v>
       </c>
       <c r="B484" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C484" t="s">
         <v>995</v>
       </c>
       <c r="D484" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E484" t="s">
         <v>10</v>
       </c>
       <c r="F484">
-        <v>215</v>
+        <v>182</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
@@ -13204,19 +13168,19 @@
         <v>996</v>
       </c>
       <c r="B485" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C485" t="s">
         <v>997</v>
       </c>
       <c r="D485" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E485" t="s">
         <v>10</v>
       </c>
       <c r="F485">
-        <v>100</v>
+        <v>192</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
@@ -13224,19 +13188,19 @@
         <v>998</v>
       </c>
       <c r="B486" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C486" t="s">
         <v>999</v>
       </c>
       <c r="D486" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E486" t="s">
         <v>10</v>
       </c>
       <c r="F486">
-        <v>145</v>
+        <v>167</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
@@ -13244,19 +13208,19 @@
         <v>1000</v>
       </c>
       <c r="B487" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C487" t="s">
         <v>1001</v>
       </c>
       <c r="D487" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E487" t="s">
         <v>10</v>
       </c>
       <c r="F487">
-        <v>165</v>
+        <v>298</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
@@ -13264,19 +13228,19 @@
         <v>1002</v>
       </c>
       <c r="B488" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C488" t="s">
         <v>1003</v>
       </c>
       <c r="D488" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E488" t="s">
         <v>10</v>
       </c>
       <c r="F488">
-        <v>235</v>
+        <v>109</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
@@ -13284,19 +13248,19 @@
         <v>1004</v>
       </c>
       <c r="B489" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C489" t="s">
         <v>1005</v>
       </c>
       <c r="D489" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E489" t="s">
         <v>10</v>
       </c>
       <c r="F489">
-        <v>255</v>
+        <v>288</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
@@ -13304,19 +13268,19 @@
         <v>1006</v>
       </c>
       <c r="B490" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C490" t="s">
         <v>1007</v>
       </c>
       <c r="D490" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E490" t="s">
         <v>10</v>
       </c>
       <c r="F490">
-        <v>210</v>
+        <v>286</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
@@ -13324,19 +13288,19 @@
         <v>1008</v>
       </c>
       <c r="B491" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C491" t="s">
         <v>1009</v>
       </c>
       <c r="D491" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E491" t="s">
         <v>10</v>
       </c>
       <c r="F491">
-        <v>174</v>
+        <v>103</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
@@ -13344,19 +13308,19 @@
         <v>1010</v>
       </c>
       <c r="B492" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C492" t="s">
         <v>1011</v>
       </c>
       <c r="D492" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E492" t="s">
         <v>10</v>
       </c>
       <c r="F492">
-        <v>231</v>
+        <v>292</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
@@ -13364,19 +13328,19 @@
         <v>1012</v>
       </c>
       <c r="B493" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C493" t="s">
         <v>1013</v>
       </c>
       <c r="D493" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E493" t="s">
         <v>10</v>
       </c>
       <c r="F493">
-        <v>229</v>
+        <v>243</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
@@ -13384,19 +13348,19 @@
         <v>1014</v>
       </c>
       <c r="B494" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C494" t="s">
         <v>1015</v>
       </c>
       <c r="D494" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E494" t="s">
         <v>10</v>
       </c>
       <c r="F494">
-        <v>108</v>
+        <v>287</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
@@ -13404,19 +13368,19 @@
         <v>1016</v>
       </c>
       <c r="B495" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C495" t="s">
         <v>1017</v>
       </c>
       <c r="D495" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E495" t="s">
         <v>10</v>
       </c>
       <c r="F495">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
@@ -13424,19 +13388,19 @@
         <v>1018</v>
       </c>
       <c r="B496" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C496" t="s">
         <v>1019</v>
       </c>
       <c r="D496" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E496" t="s">
         <v>10</v>
       </c>
       <c r="F496">
-        <v>239</v>
+        <v>121</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
@@ -13444,7 +13408,7 @@
         <v>1020</v>
       </c>
       <c r="B497" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C497" t="s">
         <v>1021</v>
@@ -13456,7 +13420,7 @@
         <v>10</v>
       </c>
       <c r="F497">
-        <v>127</v>
+        <v>265</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
@@ -13464,7 +13428,7 @@
         <v>1022</v>
       </c>
       <c r="B498" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="C498" t="s">
         <v>1023</v>
@@ -13476,127 +13440,7 @@
         <v>10</v>
       </c>
       <c r="F498">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A499" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B499" t="s">
-        <v>936</v>
-      </c>
-      <c r="C499" t="s">
-        <v>1025</v>
-      </c>
-      <c r="D499" t="s">
-        <v>16</v>
-      </c>
-      <c r="E499" t="s">
-        <v>10</v>
-      </c>
-      <c r="F499">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A500" t="s">
-        <v>1026</v>
-      </c>
-      <c r="B500" t="s">
-        <v>936</v>
-      </c>
-      <c r="C500" t="s">
-        <v>1027</v>
-      </c>
-      <c r="D500" t="s">
-        <v>9</v>
-      </c>
-      <c r="E500" t="s">
-        <v>10</v>
-      </c>
-      <c r="F500">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A501" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B501" t="s">
-        <v>936</v>
-      </c>
-      <c r="C501" t="s">
-        <v>1029</v>
-      </c>
-      <c r="D501" t="s">
-        <v>13</v>
-      </c>
-      <c r="E501" t="s">
-        <v>10</v>
-      </c>
-      <c r="F501">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A502" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B502" t="s">
-        <v>936</v>
-      </c>
-      <c r="C502" t="s">
-        <v>1031</v>
-      </c>
-      <c r="D502" t="s">
-        <v>16</v>
-      </c>
-      <c r="E502" t="s">
-        <v>10</v>
-      </c>
-      <c r="F502">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A503" t="s">
-        <v>1032</v>
-      </c>
-      <c r="B503" t="s">
-        <v>936</v>
-      </c>
-      <c r="C503" t="s">
-        <v>1033</v>
-      </c>
-      <c r="D503" t="s">
-        <v>9</v>
-      </c>
-      <c r="E503" t="s">
-        <v>10</v>
-      </c>
-      <c r="F503">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A504" t="s">
-        <v>1034</v>
-      </c>
-      <c r="B504" t="s">
-        <v>936</v>
-      </c>
-      <c r="C504" t="s">
-        <v>1035</v>
-      </c>
-      <c r="D504" t="s">
-        <v>13</v>
-      </c>
-      <c r="E504" t="s">
-        <v>10</v>
-      </c>
-      <c r="F504">
-        <v>264</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
